--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="1028">
   <si>
     <t xml:space="preserve">Master row</t>
   </si>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">10_F0_68_0C_06_D6</t>
   </si>
   <si>
-    <t xml:space="preserve">Via LT2-1 port 1/1/23 (their 1/1/12), confirmed by LLDP</t>
+    <t xml:space="preserve">Via LT2-1 port 1/1/23 (their 1/1/12), confirmed by LLDP. New VLANs tagged on LT2-1 1/1/23 on 6 Oct 2026</t>
   </si>
   <si>
     <t xml:space="preserve">switch-200V-LT2-3</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">10_F0_68_0B_D2_3E</t>
   </si>
   <si>
-    <t xml:space="preserve">Via LT2-1 port 1/1/24 (their 1/1/12), confirmed by LLDP</t>
+    <t xml:space="preserve">Via LT2-1 port 1/1/24 (their 1/1/12), confirmed by LLDP. New VLANs tagged on LT2-1 1/1/24 on 6 Oct 2026</t>
   </si>
   <si>
     <t xml:space="preserve">switch-200V-8</t>
@@ -2435,25 +2435,22 @@
     <t xml:space="preserve">LLDP: CLA-TAN3130059J (NUC, MAC 48:21:0B:56:AC:A4), not in device list</t>
   </si>
   <si>
-    <t xml:space="preserve">100,1212,1213,1230,1240,1250,1271,1272,1273</t>
+    <t xml:space="preserve">100,1212,1213,1230,1240,1250,1271,1272,1273,2000,2010,2020,2100,2200,2300,2310,2320,2400,2500,2510,2520,2530,2600,2700,2800,2810,2900,2950,2951,2952,2953</t>
   </si>
   <si>
     <t xml:space="preserve">10:F0:68:0C:06:E1, 10:F0:68:0C:06:D6</t>
   </si>
   <si>
-    <t xml:space="preserve">Uplink to switch-200V-LT2-2 (LLDP)</t>
+    <t xml:space="preserve">Uplink to switch-200V-LT2-2 (LLDP). 22 new VLANs (2000-2953) tagged 6 Oct 2026, ahead of cutover</t>
   </si>
   <si>
     <t xml:space="preserve">10:F0:68:0B:D2:49, 10:F0:68:0B:D2:3E, AC:B4:80:F1:61:7F</t>
   </si>
   <si>
-    <t xml:space="preserve">Uplink to switch-200V-LT2-3 (LLDP)</t>
+    <t xml:space="preserve">Uplink to switch-200V-LT2-3 (LLDP). 22 new VLANs (2000-2953) tagged 6 Oct 2026, ahead of cutover</t>
   </si>
   <si>
     <t xml:space="preserve">1212,1213,1230,1250,1271,1272,1273,2000,2010,2020,2100,2200,2300,2310,2320,2400,2500,2510,2520,2530,2600,2700,2800,2810,2900,2950,2951,2952,2953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100,1212,1213,1230,1240,1250,1271,1272,1273,2000,2010,2020,2100,2200,2300,2310,2320,2400,2500,2510,2520,2530,2600,2700,2800,2810,2900,2950,2951,2952,2953</t>
   </si>
   <si>
     <t xml:space="preserve">1240 (200v_staff)</t>
@@ -17241,7 +17238,7 @@
         <v>794</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
@@ -17259,13 +17256,13 @@
         <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
@@ -17281,13 +17278,13 @@
         <v>71</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0</v>
@@ -17303,13 +17300,13 @@
         <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
@@ -17325,19 +17322,19 @@
         <v>22</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>792</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H37" s="7"/>
     </row>
@@ -17349,13 +17346,13 @@
         <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
@@ -17371,13 +17368,13 @@
         <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -17393,13 +17390,13 @@
         <v>35</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
@@ -17415,13 +17412,13 @@
         <v>38</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0</v>
@@ -17437,13 +17434,13 @@
         <v>99</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>0</v>
@@ -17459,13 +17456,13 @@
         <v>41</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>0</v>
@@ -17481,13 +17478,13 @@
         <v>44</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>792</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
@@ -17509,7 +17506,7 @@
         <v>794</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
@@ -17533,7 +17530,7 @@
         <v>794</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>0</v>
@@ -17551,19 +17548,19 @@
         <v>85</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H47" s="7"/>
     </row>
@@ -17575,22 +17572,22 @@
         <v>99</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>814</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17607,7 +17604,7 @@
         <v>794</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
@@ -17625,7 +17622,7 @@
         <v>44</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>16</v>
@@ -17651,7 +17648,7 @@
         <v>794</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>0</v>
@@ -17688,7 +17685,7 @@
         <v>80</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>23</v>
@@ -17708,7 +17705,7 @@
         <v>80</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>15</v>
@@ -17721,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H54" s="7"/>
     </row>
@@ -17763,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H56" s="7"/>
     </row>
@@ -17845,7 +17842,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H60" s="7"/>
     </row>
@@ -17874,7 +17871,7 @@
         <v>80</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>219</v>
@@ -17894,7 +17891,7 @@
         <v>80</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>219</v>
@@ -17907,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H63" s="7"/>
     </row>
@@ -17916,7 +17913,7 @@
         <v>80</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>219</v>
@@ -17936,7 +17933,7 @@
         <v>80</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>219</v>
@@ -18099,10 +18096,10 @@
         <v>590</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="n">
@@ -18119,17 +18116,17 @@
         <v>592</v>
       </c>
       <c r="C74" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>826</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>827</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H74" s="7"/>
     </row>
@@ -18151,7 +18148,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H75" s="7"/>
     </row>
@@ -18173,7 +18170,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H76" s="7"/>
     </row>
@@ -18195,7 +18192,7 @@
         <v>1</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H77" s="7"/>
     </row>
@@ -18210,7 +18207,7 @@
         <v>792</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4" t="n">
@@ -18218,7 +18215,7 @@
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18232,7 +18229,7 @@
         <v>792</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4" t="n">
@@ -18240,7 +18237,7 @@
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18254,7 +18251,7 @@
         <v>792</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="4" t="n">
@@ -18262,7 +18259,7 @@
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18276,7 +18273,7 @@
         <v>792</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4" t="n">
@@ -18284,7 +18281,7 @@
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18298,7 +18295,7 @@
         <v>792</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4" t="n">
@@ -18306,7 +18303,7 @@
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18314,13 +18311,13 @@
         <v>80</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>792</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4" t="n">
@@ -18328,7 +18325,7 @@
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18336,7 +18333,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>219</v>
@@ -18362,7 +18359,7 @@
         <v>792</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4" t="n">
@@ -18370,7 +18367,7 @@
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18384,7 +18381,7 @@
         <v>792</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4" t="n">
@@ -18392,7 +18389,7 @@
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18400,13 +18397,13 @@
         <v>80</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>792</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4" t="n">
@@ -18414,7 +18411,7 @@
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18428,7 +18425,7 @@
         <v>792</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4" t="n">
@@ -18436,7 +18433,7 @@
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18450,7 +18447,7 @@
         <v>792</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4" t="n">
@@ -18458,7 +18455,7 @@
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18472,7 +18469,7 @@
         <v>792</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4" t="n">
@@ -18480,7 +18477,7 @@
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18494,7 +18491,7 @@
         <v>792</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4" t="n">
@@ -18502,7 +18499,7 @@
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18516,17 +18513,17 @@
         <v>792</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="H92" s="4" t="s">
         <v>849</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18540,7 +18537,7 @@
         <v>792</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="4" t="n">
@@ -18548,7 +18545,7 @@
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18562,7 +18559,7 @@
         <v>792</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4" t="n">
@@ -18570,7 +18567,7 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18584,7 +18581,7 @@
         <v>792</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4" t="n">
@@ -18592,7 +18589,7 @@
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18606,7 +18603,7 @@
         <v>792</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4" t="n">
@@ -18614,7 +18611,7 @@
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18628,7 +18625,7 @@
         <v>792</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4" t="n">
@@ -18636,7 +18633,7 @@
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18650,7 +18647,7 @@
         <v>792</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="n">
@@ -18658,7 +18655,7 @@
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18672,7 +18669,7 @@
         <v>792</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4" t="n">
@@ -18680,7 +18677,7 @@
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18694,7 +18691,7 @@
         <v>792</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4" t="n">
@@ -18702,7 +18699,7 @@
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18770,7 +18767,7 @@
         <v>80</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>219</v>
@@ -18790,7 +18787,7 @@
         <v>80</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>219</v>
@@ -18810,7 +18807,7 @@
         <v>80</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>219</v>
@@ -18823,7 +18820,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H106" s="7"/>
     </row>
@@ -18832,20 +18829,20 @@
         <v>80</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="D107" s="7" t="s">
         <v>826</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>827</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H107" s="7"/>
     </row>
@@ -18867,7 +18864,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H108" s="7"/>
     </row>
@@ -18896,7 +18893,7 @@
         <v>80</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>23</v>
@@ -18916,7 +18913,7 @@
         <v>80</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>23</v>
@@ -18929,7 +18926,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H111" s="7"/>
     </row>
@@ -18958,7 +18955,7 @@
         <v>80</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>23</v>
@@ -18978,7 +18975,7 @@
         <v>80</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>23</v>
@@ -18998,7 +18995,7 @@
         <v>80</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>23</v>
@@ -19018,7 +19015,7 @@
         <v>80</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>23</v>
@@ -19078,7 +19075,7 @@
         <v>80</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>23</v>
@@ -19091,7 +19088,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H119" s="7"/>
     </row>
@@ -19140,7 +19137,7 @@
         <v>80</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>23</v>
@@ -19153,7 +19150,7 @@
         <v>1</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H122" s="7"/>
     </row>
@@ -19162,7 +19159,7 @@
         <v>80</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>23</v>
@@ -19175,7 +19172,7 @@
         <v>1</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H123" s="7"/>
     </row>
@@ -19184,7 +19181,7 @@
         <v>80</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>23</v>
@@ -19224,7 +19221,7 @@
         <v>80</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>23</v>
@@ -19244,7 +19241,7 @@
         <v>80</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>23</v>
@@ -19277,7 +19274,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H128" s="7"/>
     </row>
@@ -19286,7 +19283,7 @@
         <v>80</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>23</v>
@@ -19315,7 +19312,7 @@
         <v>16</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>0</v>
@@ -19341,7 +19338,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H131" s="7"/>
     </row>
@@ -19423,7 +19420,7 @@
         <v>1</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H135" s="7"/>
     </row>
@@ -19472,7 +19469,7 @@
         <v>286</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>23</v>
@@ -19492,7 +19489,7 @@
         <v>286</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>15</v>
@@ -19505,7 +19502,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H139" s="7"/>
     </row>
@@ -19514,7 +19511,7 @@
         <v>286</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>148</v>
@@ -19587,7 +19584,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H143" s="7"/>
     </row>
@@ -19596,7 +19593,7 @@
         <v>286</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>219</v>
@@ -19616,7 +19613,7 @@
         <v>286</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>219</v>
@@ -19636,7 +19633,7 @@
         <v>286</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>219</v>
@@ -19656,7 +19653,7 @@
         <v>286</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>219</v>
@@ -19669,7 +19666,7 @@
         <v>1</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H147" s="7"/>
     </row>
@@ -19678,7 +19675,7 @@
         <v>286</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>219</v>
@@ -19798,7 +19795,7 @@
         <v>286</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>219</v>
@@ -19818,7 +19815,7 @@
         <v>286</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>219</v>
@@ -19871,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H157" s="7"/>
     </row>
@@ -20080,7 +20077,7 @@
         <v>286</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>23</v>
@@ -20100,7 +20097,7 @@
         <v>286</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>23</v>
@@ -20153,7 +20150,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H171" s="7"/>
     </row>
@@ -20162,7 +20159,7 @@
         <v>286</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>23</v>
@@ -20245,7 +20242,7 @@
         <v>650</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D176" s="7" t="s">
         <v>24</v>
@@ -20255,7 +20252,7 @@
         <v>1</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H176" s="7"/>
     </row>
@@ -20264,7 +20261,7 @@
         <v>286</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>23</v>
@@ -20284,7 +20281,7 @@
         <v>286</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>23</v>
@@ -20304,7 +20301,7 @@
         <v>286</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>23</v>
@@ -20324,7 +20321,7 @@
         <v>286</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>23</v>
@@ -20344,7 +20341,7 @@
         <v>286</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>23</v>
@@ -20357,7 +20354,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H181" s="7"/>
     </row>
@@ -20366,7 +20363,7 @@
         <v>286</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>23</v>
@@ -20386,10 +20383,10 @@
         <v>286</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>24</v>
@@ -20406,7 +20403,7 @@
         <v>286</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>23</v>
@@ -20426,7 +20423,7 @@
         <v>286</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>23</v>
@@ -20506,7 +20503,7 @@
         <v>286</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>23</v>
@@ -20526,7 +20523,7 @@
         <v>286</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>23</v>
@@ -20539,7 +20536,7 @@
         <v>1</v>
       </c>
       <c r="G190" s="7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H190" s="7"/>
     </row>
@@ -20561,7 +20558,7 @@
         <v>1</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H191" s="7"/>
     </row>
@@ -20613,7 +20610,7 @@
         <v>257</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>24</v>
@@ -20643,7 +20640,7 @@
         <v>1</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H195" s="7"/>
     </row>
@@ -20652,7 +20649,7 @@
         <v>286</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>23</v>
@@ -20672,7 +20669,7 @@
         <v>286</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>23</v>
@@ -20692,7 +20689,7 @@
         <v>286</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>23</v>
@@ -20705,7 +20702,7 @@
         <v>1</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H198" s="7"/>
     </row>
@@ -20714,7 +20711,7 @@
         <v>286</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>23</v>
@@ -20754,7 +20751,7 @@
         <v>286</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>23</v>
@@ -20774,7 +20771,7 @@
         <v>286</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>23</v>
@@ -20794,7 +20791,7 @@
         <v>286</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>23</v>
@@ -20823,7 +20820,7 @@
         <v>792</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>0</v>
@@ -20845,7 +20842,7 @@
         <v>792</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F205" s="2" t="n">
         <v>0</v>
@@ -20867,7 +20864,7 @@
         <v>794</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F206" s="6" t="n">
         <v>0</v>
@@ -20891,7 +20888,7 @@
         <v>792</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>0</v>
@@ -20913,7 +20910,7 @@
         <v>792</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>0</v>
@@ -20935,7 +20932,7 @@
         <v>794</v>
       </c>
       <c r="E209" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>0</v>
@@ -20959,7 +20956,7 @@
         <v>792</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>0</v>
@@ -20981,7 +20978,7 @@
         <v>792</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>0</v>
@@ -21003,7 +21000,7 @@
         <v>792</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -21025,7 +21022,7 @@
         <v>792</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>0</v>
@@ -21047,13 +21044,13 @@
         <v>792</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F214" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H214" s="7"/>
     </row>
@@ -21071,7 +21068,7 @@
         <v>792</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>0</v>
@@ -21093,7 +21090,7 @@
         <v>792</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>0</v>
@@ -21106,7 +21103,7 @@
         <v>473</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>219</v>
@@ -21115,7 +21112,7 @@
         <v>792</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>0</v>
@@ -21159,7 +21156,7 @@
         <v>792</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>0</v>
@@ -21181,7 +21178,7 @@
         <v>792</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F220" s="2" t="n">
         <v>0</v>
@@ -21203,7 +21200,7 @@
         <v>792</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F221" s="2" t="n">
         <v>0</v>
@@ -21225,7 +21222,7 @@
         <v>792</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>0</v>
@@ -21247,7 +21244,7 @@
         <v>792</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F223" s="2" t="n">
         <v>0</v>
@@ -21260,7 +21257,7 @@
         <v>473</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>219</v>
@@ -21269,7 +21266,7 @@
         <v>792</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>0</v>
@@ -21282,7 +21279,7 @@
         <v>473</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>219</v>
@@ -21291,7 +21288,7 @@
         <v>792</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F225" s="2" t="n">
         <v>0</v>
@@ -21304,7 +21301,7 @@
         <v>473</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>219</v>
@@ -21313,7 +21310,7 @@
         <v>792</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>0</v>
@@ -21326,7 +21323,7 @@
         <v>473</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>219</v>
@@ -21426,7 +21423,7 @@
         <v>473</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>219</v>
@@ -21446,7 +21443,7 @@
         <v>473</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>219</v>
@@ -21466,7 +21463,7 @@
         <v>473</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>219</v>
@@ -21486,7 +21483,7 @@
         <v>473</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>219</v>
@@ -21506,7 +21503,7 @@
         <v>473</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>219</v>
@@ -21555,7 +21552,7 @@
         <v>794</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F238" s="6" t="n">
         <v>0</v>
@@ -21576,7 +21573,7 @@
         <v>16</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" s="2" t="n">
@@ -21610,7 +21607,7 @@
         <v>473</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>219</v>
@@ -21623,7 +21620,7 @@
         <v>1</v>
       </c>
       <c r="G241" s="7" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H241" s="7"/>
     </row>
@@ -21632,7 +21629,7 @@
         <v>473</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>23</v>
@@ -21652,7 +21649,7 @@
         <v>473</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>219</v>
@@ -21672,7 +21669,7 @@
         <v>473</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>219</v>
@@ -21692,7 +21689,7 @@
         <v>473</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>219</v>
@@ -21712,7 +21709,7 @@
         <v>473</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>219</v>
@@ -21732,7 +21729,7 @@
         <v>473</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>219</v>
@@ -21752,7 +21749,7 @@
         <v>473</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>219</v>
@@ -21772,7 +21769,7 @@
         <v>473</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>219</v>
@@ -21792,7 +21789,7 @@
         <v>473</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>219</v>
@@ -21812,7 +21809,7 @@
         <v>473</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>219</v>
@@ -21832,7 +21829,7 @@
         <v>473</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>219</v>
@@ -21852,7 +21849,7 @@
         <v>473</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>219</v>
@@ -21872,7 +21869,7 @@
         <v>473</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C254" s="7" t="s">
         <v>219</v>
@@ -21885,7 +21882,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H254" s="7"/>
     </row>
@@ -21894,7 +21891,7 @@
         <v>473</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>219</v>
@@ -21934,7 +21931,7 @@
         <v>473</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>219</v>
@@ -22034,7 +22031,7 @@
         <v>473</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>219</v>
@@ -22054,7 +22051,7 @@
         <v>473</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>219</v>
@@ -22074,7 +22071,7 @@
         <v>473</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>219</v>
@@ -22154,7 +22151,7 @@
         <v>473</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>219</v>
@@ -22294,7 +22291,7 @@
         <v>473</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>219</v>
@@ -22414,7 +22411,7 @@
         <v>473</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>219</v>
@@ -22454,7 +22451,7 @@
         <v>473</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>219</v>
@@ -22514,7 +22511,7 @@
         <v>473</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>219</v>
@@ -22547,7 +22544,7 @@
         <v>1</v>
       </c>
       <c r="G287" s="7" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H287" s="7"/>
     </row>
@@ -22616,7 +22613,7 @@
         <v>473</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>15</v>
@@ -22625,7 +22622,7 @@
         <v>16</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F291" s="2" t="n">
         <v>0</v>
@@ -22698,7 +22695,7 @@
         <v>473</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>219</v>
@@ -22738,7 +22735,7 @@
         <v>473</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>219</v>
@@ -22818,7 +22815,7 @@
         <v>473</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>219</v>
@@ -22851,7 +22848,7 @@
         <v>1</v>
       </c>
       <c r="G302" s="7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H302" s="7"/>
     </row>
@@ -22860,7 +22857,7 @@
         <v>473</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>219</v>
@@ -22880,7 +22877,7 @@
         <v>473</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>219</v>
@@ -22900,7 +22897,7 @@
         <v>473</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>219</v>
@@ -22920,7 +22917,7 @@
         <v>473</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>219</v>
@@ -22940,7 +22937,7 @@
         <v>473</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>219</v>
@@ -22960,7 +22957,7 @@
         <v>473</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>219</v>
@@ -22980,7 +22977,7 @@
         <v>473</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>219</v>
@@ -23000,7 +22997,7 @@
         <v>473</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>219</v>
@@ -23020,7 +23017,7 @@
         <v>473</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>219</v>
@@ -23040,7 +23037,7 @@
         <v>473</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>219</v>
@@ -23060,7 +23057,7 @@
         <v>473</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>219</v>
@@ -23080,7 +23077,7 @@
         <v>473</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>219</v>
@@ -23100,7 +23097,7 @@
         <v>473</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>219</v>
@@ -23120,7 +23117,7 @@
         <v>473</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>219</v>
@@ -23140,7 +23137,7 @@
         <v>473</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>219</v>
@@ -23160,7 +23157,7 @@
         <v>473</v>
       </c>
       <c r="B318" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C318" s="7" t="s">
         <v>219</v>
@@ -23173,7 +23170,7 @@
         <v>1</v>
       </c>
       <c r="G318" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H318" s="7"/>
     </row>
@@ -23182,7 +23179,7 @@
         <v>473</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>219</v>
@@ -23202,7 +23199,7 @@
         <v>473</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>219</v>
@@ -23222,7 +23219,7 @@
         <v>473</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>23</v>
@@ -23242,7 +23239,7 @@
         <v>473</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>219</v>
@@ -23262,7 +23259,7 @@
         <v>473</v>
       </c>
       <c r="B323" s="7" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C323" s="7" t="s">
         <v>219</v>
@@ -23275,7 +23272,7 @@
         <v>1</v>
       </c>
       <c r="G323" s="7" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H323" s="7"/>
     </row>
@@ -23284,7 +23281,7 @@
         <v>473</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>23</v>
@@ -23304,7 +23301,7 @@
         <v>473</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>219</v>
@@ -23324,7 +23321,7 @@
         <v>473</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>23</v>
@@ -23344,7 +23341,7 @@
         <v>473</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>219</v>
@@ -23364,7 +23361,7 @@
         <v>473</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C328" s="7" t="s">
         <v>219</v>
@@ -23377,7 +23374,7 @@
         <v>1</v>
       </c>
       <c r="G328" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H328" s="7"/>
     </row>
@@ -23386,7 +23383,7 @@
         <v>473</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>219</v>
@@ -23406,7 +23403,7 @@
         <v>473</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>219</v>
@@ -23426,7 +23423,7 @@
         <v>473</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>219</v>
@@ -23446,7 +23443,7 @@
         <v>473</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>219</v>
@@ -23466,7 +23463,7 @@
         <v>473</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>219</v>
@@ -23486,7 +23483,7 @@
         <v>473</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>219</v>
@@ -23506,7 +23503,7 @@
         <v>473</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>219</v>
@@ -23526,7 +23523,7 @@
         <v>473</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>219</v>
@@ -23546,7 +23543,7 @@
         <v>473</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>219</v>
@@ -23566,7 +23563,7 @@
         <v>473</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C338" s="6" t="s">
         <v>793</v>
@@ -23575,7 +23572,7 @@
         <v>794</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F338" s="6" t="n">
         <v>0</v>
@@ -23590,7 +23587,7 @@
         <v>473</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>219</v>
@@ -23610,7 +23607,7 @@
         <v>473</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>219</v>
@@ -23630,7 +23627,7 @@
         <v>473</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>23</v>
@@ -23650,7 +23647,7 @@
         <v>473</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>219</v>
@@ -23670,7 +23667,7 @@
         <v>473</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>219</v>
@@ -23690,7 +23687,7 @@
         <v>473</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>219</v>
@@ -23710,7 +23707,7 @@
         <v>473</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>219</v>
@@ -23730,7 +23727,7 @@
         <v>473</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>219</v>
@@ -23750,7 +23747,7 @@
         <v>473</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>219</v>
@@ -23770,7 +23767,7 @@
         <v>473</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>219</v>
@@ -23790,7 +23787,7 @@
         <v>473</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>219</v>
@@ -23810,7 +23807,7 @@
         <v>473</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>219</v>
@@ -23830,7 +23827,7 @@
         <v>473</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>219</v>
@@ -23850,7 +23847,7 @@
         <v>473</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>219</v>
@@ -23870,7 +23867,7 @@
         <v>473</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>219</v>
@@ -23890,7 +23887,7 @@
         <v>473</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>219</v>
@@ -23910,7 +23907,7 @@
         <v>473</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>219</v>
@@ -23930,7 +23927,7 @@
         <v>473</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>219</v>
@@ -23950,7 +23947,7 @@
         <v>473</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>219</v>
@@ -23970,7 +23967,7 @@
         <v>473</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>23</v>
@@ -23990,7 +23987,7 @@
         <v>473</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>23</v>
@@ -24010,7 +24007,7 @@
         <v>473</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>219</v>
@@ -24030,7 +24027,7 @@
         <v>473</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>219</v>
@@ -24050,7 +24047,7 @@
         <v>473</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>219</v>
@@ -24114,7 +24111,7 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24125,10 +24122,10 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>999</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -24137,7 +24134,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24151,16 +24148,16 @@
         <v>177</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>1002</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24174,16 +24171,16 @@
         <v>177</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24197,16 +24194,16 @@
         <v>168</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24220,16 +24217,16 @@
         <v>168</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24243,16 +24240,16 @@
         <v>168</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
   </sheetData>
@@ -24282,10 +24279,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>1007</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24294,7 +24291,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B3" s="9" t="n">
         <f aca="false">COUNTA('200V Devices'!C2:C393)</f>
@@ -24303,7 +24300,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B4" s="9" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"Done (pilot)")</f>
@@ -24312,7 +24309,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"To do")</f>
@@ -24321,7 +24318,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF('200V Devices'!J2:J393,"Matched from 200V tab")</f>
@@ -24330,7 +24327,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTA('Not found'!C2:C7)</f>
@@ -24339,7 +24336,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">B3+B7</f>
@@ -24352,10 +24349,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>1015</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24409,29 +24406,29 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>1018</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>1020</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTA('Ports without device'!A2:A362)</f>
@@ -24440,7 +24437,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,"&gt;0")</f>
@@ -24449,7 +24446,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,0)</f>
@@ -24458,7 +24455,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">COUNTIF('Ports without device'!H2:H362,"Pilot staff outlet*")</f>
@@ -24467,7 +24464,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B25" s="9" t="n">
         <f aca="false">COUNTIF('Ports without device'!C2:C362,"None (tagged only)")</f>
@@ -24476,10 +24473,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>1027</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>1028</v>
       </c>
     </row>
   </sheetData>

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Comments</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Device list: ports filled in by Claude</t>
+    <t xml:space="preserve">1. Device list: ports filled in by script</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -630,13 +630,25 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">VLANs 2600 and 2700 have no spanning-tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other VLANs on lv6, and 2600/2700 on lv3 and lv4, have spanning-tree enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add spanning-tree to 2600 and 2700 on lv6</t>
+    <t xml:space="preserve">Raise spanning-tree limit, then enable spanning-tree on 2600 and 2700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lv6 has 35 VLANs but spanning-tree on only 32, the ICX default maximum, so 2600 (CCTV), 2700 (AV) and 2953 run without spanning-tree. lv4 already has system-max spanning-tree 40 configured but still shows 32, which suggests the new limit only applies after a reload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run on lv6:
+configure terminal
+system-max spanning-tree 128
+write memory
+Then reload in a maintenance window, then:
+configure terminal
+vlan 2600
+ spanning-tree
+ exit
+vlan 2700
+ spanning-tree
+ exit
+write memory</t>
   </si>
   <si>
     <t xml:space="preserve">VLAN 100 tagged on every port (1/1/1-1/1/12)</t>
@@ -6192,7 +6204,7 @@
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
     </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>80</v>
       </c>

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'200V Devices'!$A$1:$J$393</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Not found'!$A$1:$G$7</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Ports without device'!$A$1:$H$362</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Switches!$A$1:$G$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Switches!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5750" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5761" uniqueCount="1185">
   <si>
     <t xml:space="preserve">200V migration: items for review</t>
   </si>
@@ -2818,6 +2818,9 @@
     <t xml:space="preserve">200V devices</t>
   </si>
   <si>
+    <t xml:space="preserve">Management IP</t>
+  </si>
+  <si>
     <t xml:space="preserve">trinity200V-core</t>
   </si>
   <si>
@@ -2833,6 +2836,9 @@
     <t xml:space="preserve">n/a</t>
   </si>
   <si>
+    <t xml:space="preserve">10.20.8.2 (ve 1960)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Access</t>
   </si>
   <si>
@@ -2845,12 +2851,18 @@
     <t xml:space="preserve">lag 3 (lvl3)</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.22</t>
+  </si>
+  <si>
     <t xml:space="preserve">80_F0_CF_37_FD_84</t>
   </si>
   <si>
     <t xml:space="preserve">lag 2 (lvl4)</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.21</t>
+  </si>
+  <si>
     <t xml:space="preserve">7 x ICX8200 stack</t>
   </si>
   <si>
@@ -2860,6 +2872,9 @@
     <t xml:space="preserve">lag 1 (lvl6)</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.11</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 x ICX8200-24P</t>
   </si>
   <si>
@@ -2869,6 +2884,9 @@
     <t xml:space="preserve">lag 5 (LT01), LT2-1 ports 1/2/1-1/2/2 to core 1/1/5 + 2/1/5 (LLDP)</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.12</t>
+  </si>
+  <si>
     <t xml:space="preserve">switch-200V-LT2-2</t>
   </si>
   <si>
@@ -2881,25 +2899,40 @@
     <t xml:space="preserve">Via LT2-1 port 1/1/23 (their 1/1/12), confirmed by LLDP. New VLANs tagged on LT2-1 1/1/23 on 6 Oct 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.13</t>
+  </si>
+  <si>
     <t xml:space="preserve">10_F0_68_0B_D2_3E</t>
   </si>
   <si>
     <t xml:space="preserve">Via LT2-1 port 1/1/24 (their 1/1/12), confirmed by LLDP. New VLANs tagged on LT2-1 1/1/24 on 6 Oct 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.14</t>
+  </si>
+  <si>
     <t xml:space="preserve">10_F0_68_0B_D2_2C</t>
   </si>
   <si>
     <t xml:space="preserve">lag 4 (v08)</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.16</t>
+  </si>
+  <si>
     <t xml:space="preserve">10_F0_68_0B_D2_62</t>
   </si>
   <si>
     <t xml:space="preserve">lag 6 (SW6.03)</t>
   </si>
   <si>
+    <t xml:space="preserve">192.168.122.15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: the management IP addresses of the switches are not changing as part of this migration. Access switches stay on VLAN 100 (ve 100, 192.168.122.0/22); the core stays on ve 1960.</t>
   </si>
   <si>
     <t xml:space="preserve">Untagged VLAN</t>
@@ -3776,15 +3809,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -18949,7 +18982,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="28"/>
@@ -18958,6 +18991,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18982,28 +19016,34 @@
       <c r="G1" s="3" t="s">
         <v>227</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>927</v>
+        <v>928</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19011,16 +19051,16 @@
         <v>87</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F3" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A3)</f>
@@ -19030,22 +19070,25 @@
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A3,'200V Devices'!I2:I393,"To do")</f>
         <v>84</v>
       </c>
+      <c r="H3" s="7" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="F4" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A4)</f>
@@ -19055,22 +19098,25 @@
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A4,'200V Devices'!I2:I393,"To do")</f>
         <v>89</v>
       </c>
+      <c r="H4" s="7" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="F5" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A5)</f>
@@ -19080,22 +19126,25 @@
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A5,'200V Devices'!I2:I393,"To do")</f>
         <v>158</v>
       </c>
+      <c r="H5" s="7" t="s">
+        <v>941</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A6)</f>
@@ -19105,22 +19154,25 @@
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A6,'200V Devices'!I2:I393,"To do")</f>
         <v>16</v>
       </c>
+      <c r="H6" s="7" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="F7" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A7)</f>
@@ -19129,6 +19181,9 @@
       <c r="G7" s="7" t="n">
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A7,'200V Devices'!I2:I393,"To do")</f>
         <v>0</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19136,16 +19191,16 @@
         <v>81</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="F8" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A8)</f>
@@ -19154,6 +19209,9 @@
       <c r="G8" s="7" t="n">
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A8,'200V Devices'!I2:I393,"To do")</f>
         <v>0</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>953</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19161,16 +19219,16 @@
         <v>196</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="F9" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A9)</f>
@@ -19179,6 +19237,9 @@
       <c r="G9" s="7" t="n">
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A9,'200V Devices'!I2:I393,"To do")</f>
         <v>0</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19186,16 +19247,16 @@
         <v>64</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="F10" s="7" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A10)</f>
@@ -19205,10 +19266,13 @@
         <f aca="false">COUNTIFS('200V Devices'!E2:E393,A10,'200V Devices'!I2:I393,"To do")</f>
         <v>6</v>
       </c>
+      <c r="H10" s="7" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -19222,9 +19286,15 @@
         <f aca="false">SUM(G2:G10)</f>
         <v>353</v>
       </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>961</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:H10"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -19262,22 +19332,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>219</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19291,7 +19361,7 @@
         <v>405</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7" t="n">
@@ -19311,7 +19381,7 @@
         <v>405</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="n">
@@ -19331,7 +19401,7 @@
         <v>405</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="n">
@@ -19351,7 +19421,7 @@
         <v>405</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="n">
@@ -19371,7 +19441,7 @@
         <v>405</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="n">
@@ -19411,7 +19481,7 @@
         <v>405</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="n">
@@ -19431,7 +19501,7 @@
         <v>405</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="n">
@@ -19451,7 +19521,7 @@
         <v>405</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="n">
@@ -19471,7 +19541,7 @@
         <v>405</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="n">
@@ -19491,7 +19561,7 @@
         <v>405</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="n">
@@ -19501,27 +19571,27 @@
       <c r="H12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>959</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11" t="s">
-        <v>960</v>
+      <c r="C13" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>970</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19538,7 +19608,7 @@
         <v>226</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
@@ -19567,26 +19637,26 @@
       <c r="H15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12" t="n">
+      <c r="C16" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="H16" s="12"/>
+      <c r="G16" s="13" t="s">
+        <v>973</v>
+      </c>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
@@ -19609,27 +19679,27 @@
       <c r="H17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12" t="n">
+      <c r="D18" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>963</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>964</v>
+      <c r="G18" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19653,60 +19723,60 @@
       <c r="H19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>965</v>
-      </c>
-      <c r="F20" s="11" t="n">
+      <c r="C20" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>966</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>967</v>
+      <c r="G20" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>965</v>
-      </c>
-      <c r="F21" s="11" t="n">
+      <c r="C21" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>968</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>969</v>
+      <c r="G21" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>195</v>
@@ -19715,10 +19785,10 @@
         <v>405</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0</v>
@@ -19728,7 +19798,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>178</v>
@@ -19737,7 +19807,7 @@
         <v>405</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="n">
@@ -19748,7 +19818,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>85</v>
@@ -19757,7 +19827,7 @@
         <v>405</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="n">
@@ -19768,7 +19838,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>82</v>
@@ -19777,7 +19847,7 @@
         <v>405</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="n">
@@ -19788,7 +19858,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>236</v>
@@ -19797,7 +19867,7 @@
         <v>405</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="n">
@@ -19808,7 +19878,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>14</v>
@@ -19817,7 +19887,7 @@
         <v>405</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="n">
@@ -19828,7 +19898,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>18</v>
@@ -19837,7 +19907,7 @@
         <v>405</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7" t="n">
@@ -19848,7 +19918,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>21</v>
@@ -19857,7 +19927,7 @@
         <v>405</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="n">
@@ -19868,7 +19938,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>65</v>
@@ -19877,7 +19947,7 @@
         <v>405</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="n">
@@ -19888,7 +19958,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>24</v>
@@ -19897,7 +19967,7 @@
         <v>405</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="n">
@@ -19908,7 +19978,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>27</v>
@@ -19917,7 +19987,7 @@
         <v>405</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="n">
@@ -19927,27 +19997,27 @@
       <c r="H32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>940</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="A33" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>965</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11" t="s">
-        <v>960</v>
+      <c r="C33" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19958,13 +20028,13 @@
         <v>195</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>0</v>
@@ -19980,13 +20050,13 @@
         <v>178</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>0</v>
@@ -20002,13 +20072,13 @@
         <v>85</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
@@ -20017,28 +20087,28 @@
       <c r="H36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>971</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>972</v>
-      </c>
-      <c r="F37" s="12" t="n">
+      <c r="C37" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="F37" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="12" t="s">
-        <v>973</v>
-      </c>
-      <c r="H37" s="12"/>
+      <c r="G37" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="H37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
@@ -20048,13 +20118,13 @@
         <v>236</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
@@ -20070,13 +20140,13 @@
         <v>14</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>0</v>
@@ -20092,13 +20162,13 @@
         <v>18</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>0</v>
@@ -20114,13 +20184,13 @@
         <v>21</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>0</v>
@@ -20136,13 +20206,13 @@
         <v>65</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>0</v>
@@ -20158,13 +20228,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F43" s="7" t="n">
         <v>0</v>
@@ -20180,13 +20250,13 @@
         <v>27</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -20195,125 +20265,125 @@
       <c r="H44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>965</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11" t="s">
-        <v>960</v>
+      <c r="C45" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>974</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11" t="s">
-        <v>960</v>
+      <c r="C46" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>975</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>972</v>
-      </c>
-      <c r="F47" s="12" t="n">
+      <c r="C47" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="F47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="12" t="s">
-        <v>976</v>
-      </c>
-      <c r="H47" s="12"/>
+      <c r="G47" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="H47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>975</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>972</v>
-      </c>
-      <c r="F48" s="12" t="n">
+      <c r="C48" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="F48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="12" t="s">
-        <v>977</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>978</v>
+      <c r="G48" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>989</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11" t="s">
-        <v>960</v>
+      <c r="C49" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20324,7 +20394,7 @@
         <v>27</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>226</v>
@@ -20337,27 +20407,27 @@
       <c r="H50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="F51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11" t="s">
-        <v>960</v>
+      <c r="C51" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20374,7 +20444,7 @@
         <v>226</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="F52" s="7" t="n">
         <v>0</v>
@@ -20387,7 +20457,7 @@
         <v>87</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>232</v>
@@ -20403,26 +20473,26 @@
       <c r="H53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12" t="n">
+      <c r="E54" s="13"/>
+      <c r="F54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="12" t="s">
-        <v>980</v>
-      </c>
-      <c r="H54" s="12"/>
+      <c r="G54" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="H54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
@@ -20445,26 +20515,26 @@
       <c r="H55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12" t="n">
+      <c r="C56" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="12" t="s">
-        <v>981</v>
-      </c>
-      <c r="H56" s="12"/>
+      <c r="G56" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
@@ -20527,26 +20597,26 @@
       <c r="H59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12" t="n">
+      <c r="C60" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="12" t="s">
-        <v>982</v>
-      </c>
-      <c r="H60" s="12"/>
+      <c r="G60" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
@@ -20573,13 +20643,13 @@
         <v>87</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="n">
@@ -20589,26 +20659,26 @@
       <c r="H62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12" t="n">
+      <c r="D63" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="12" t="s">
-        <v>984</v>
-      </c>
-      <c r="H63" s="12"/>
+      <c r="G63" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="H63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
@@ -20621,7 +20691,7 @@
         <v>405</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="n">
@@ -20635,13 +20705,13 @@
         <v>87</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="n">
@@ -20661,7 +20731,7 @@
         <v>405</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="n">
@@ -20681,7 +20751,7 @@
         <v>405</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="n">
@@ -20701,7 +20771,7 @@
         <v>405</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="n">
@@ -20721,7 +20791,7 @@
         <v>405</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="n">
@@ -20741,7 +20811,7 @@
         <v>405</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="n">
@@ -20761,7 +20831,7 @@
         <v>405</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="n">
@@ -20781,7 +20851,7 @@
         <v>405</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="n">
@@ -20798,10 +20868,10 @@
         <v>130</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="n">
@@ -20811,92 +20881,92 @@
       <c r="H73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>986</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>987</v>
-      </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12" t="n">
+      <c r="C74" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="12" t="s">
-        <v>988</v>
-      </c>
-      <c r="H74" s="12"/>
+      <c r="G74" s="13" t="s">
+        <v>999</v>
+      </c>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="s">
+      <c r="A75" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D75" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12" t="n">
+      <c r="D75" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="12" t="s">
-        <v>989</v>
-      </c>
-      <c r="H75" s="12"/>
+      <c r="G75" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D76" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12" t="n">
+      <c r="D76" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="12" t="s">
-        <v>990</v>
-      </c>
-      <c r="H76" s="12"/>
+      <c r="G76" s="13" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H76" s="13"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12" t="n">
+      <c r="D77" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="12" t="s">
-        <v>991</v>
-      </c>
-      <c r="H77" s="12"/>
+      <c r="G77" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H77" s="13"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
@@ -20906,10 +20976,10 @@
         <v>789</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E78" s="9"/>
       <c r="F78" s="9" t="n">
@@ -20917,7 +20987,7 @@
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="9" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20928,10 +20998,10 @@
         <v>791</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E79" s="9"/>
       <c r="F79" s="9" t="n">
@@ -20939,7 +21009,7 @@
       </c>
       <c r="G79" s="9"/>
       <c r="H79" s="9" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20950,10 +21020,10 @@
         <v>793</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E80" s="9"/>
       <c r="F80" s="9" t="n">
@@ -20961,7 +21031,7 @@
       </c>
       <c r="G80" s="9"/>
       <c r="H80" s="9" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20972,10 +21042,10 @@
         <v>795</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E81" s="9"/>
       <c r="F81" s="9" t="n">
@@ -20983,7 +21053,7 @@
       </c>
       <c r="G81" s="9"/>
       <c r="H81" s="9" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20994,10 +21064,10 @@
         <v>797</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9" t="n">
@@ -21005,7 +21075,7 @@
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="9" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21016,10 +21086,10 @@
         <v>151</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9" t="n">
@@ -21027,7 +21097,7 @@
       </c>
       <c r="G83" s="9"/>
       <c r="H83" s="9" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21035,13 +21105,13 @@
         <v>87</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="n">
@@ -21058,10 +21128,10 @@
         <v>584</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E85" s="9"/>
       <c r="F85" s="9" t="n">
@@ -21069,7 +21139,7 @@
       </c>
       <c r="G85" s="9"/>
       <c r="H85" s="9" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21080,10 +21150,10 @@
         <v>132</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E86" s="9"/>
       <c r="F86" s="9" t="n">
@@ -21091,7 +21161,7 @@
       </c>
       <c r="G86" s="9"/>
       <c r="H86" s="9" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21099,13 +21169,13 @@
         <v>87</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E87" s="9"/>
       <c r="F87" s="9" t="n">
@@ -21113,7 +21183,7 @@
       </c>
       <c r="G87" s="9"/>
       <c r="H87" s="9" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21124,10 +21194,10 @@
         <v>587</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E88" s="9"/>
       <c r="F88" s="9" t="n">
@@ -21135,7 +21205,7 @@
       </c>
       <c r="G88" s="9"/>
       <c r="H88" s="9" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21146,10 +21216,10 @@
         <v>589</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9" t="n">
@@ -21157,7 +21227,7 @@
       </c>
       <c r="G89" s="9"/>
       <c r="H89" s="9" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21168,10 +21238,10 @@
         <v>803</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9" t="n">
@@ -21179,7 +21249,7 @@
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="9" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21190,10 +21260,10 @@
         <v>591</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9" t="n">
@@ -21201,7 +21271,7 @@
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="9" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21212,20 +21282,20 @@
         <v>593</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21236,10 +21306,10 @@
         <v>807</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9" t="n">
@@ -21247,7 +21317,7 @@
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="9" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21258,10 +21328,10 @@
         <v>809</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9" t="n">
@@ -21269,7 +21339,7 @@
       </c>
       <c r="G94" s="9"/>
       <c r="H94" s="9" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21280,10 +21350,10 @@
         <v>596</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9" t="n">
@@ -21291,7 +21361,7 @@
       </c>
       <c r="G95" s="9"/>
       <c r="H95" s="9" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21302,10 +21372,10 @@
         <v>812</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9" t="n">
@@ -21313,7 +21383,7 @@
       </c>
       <c r="G96" s="9"/>
       <c r="H96" s="9" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21324,10 +21394,10 @@
         <v>814</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9" t="n">
@@ -21335,7 +21405,7 @@
       </c>
       <c r="G97" s="9"/>
       <c r="H97" s="9" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21346,10 +21416,10 @@
         <v>598</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9" t="n">
@@ -21357,7 +21427,7 @@
       </c>
       <c r="G98" s="9"/>
       <c r="H98" s="9" t="s">
-        <v>1015</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21368,10 +21438,10 @@
         <v>134</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9" t="n">
@@ -21379,7 +21449,7 @@
       </c>
       <c r="G99" s="9"/>
       <c r="H99" s="9" t="s">
-        <v>1016</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21390,10 +21460,10 @@
         <v>818</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9" t="n">
@@ -21401,7 +21471,7 @@
       </c>
       <c r="G100" s="9"/>
       <c r="H100" s="9" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21415,7 +21485,7 @@
         <v>405</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="n">
@@ -21435,7 +21505,7 @@
         <v>405</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="7" t="n">
@@ -21455,7 +21525,7 @@
         <v>405</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7" t="n">
@@ -21469,13 +21539,13 @@
         <v>87</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="n">
@@ -21489,13 +21559,13 @@
         <v>87</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="n">
@@ -21505,70 +21575,70 @@
       <c r="H105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D106" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E106" s="12"/>
-      <c r="F106" s="12" t="n">
+      <c r="D106" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E106" s="13"/>
+      <c r="F106" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G106" s="12" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H106" s="12"/>
+      <c r="G106" s="13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H106" s="13"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="12" t="s">
-        <v>986</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>987</v>
-      </c>
-      <c r="E107" s="12"/>
-      <c r="F107" s="12" t="n">
+      <c r="C107" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G107" s="12" t="s">
-        <v>1021</v>
-      </c>
-      <c r="H107" s="12"/>
+      <c r="G107" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H107" s="13"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C108" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E108" s="12"/>
-      <c r="F108" s="12" t="n">
+      <c r="C108" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G108" s="12" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H108" s="12"/>
+      <c r="G108" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H108" s="13"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
@@ -21595,7 +21665,7 @@
         <v>87</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>232</v>
@@ -21611,26 +21681,26 @@
       <c r="H110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12" t="s">
+      <c r="A111" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E111" s="12"/>
-      <c r="F111" s="12" t="n">
+      <c r="C111" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G111" s="12" t="s">
-        <v>1024</v>
-      </c>
-      <c r="H111" s="12"/>
+      <c r="G111" s="13" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H111" s="13"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
@@ -21657,7 +21727,7 @@
         <v>87</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>232</v>
@@ -21677,7 +21747,7 @@
         <v>87</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>232</v>
@@ -21717,7 +21787,7 @@
         <v>87</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>1027</v>
+        <v>1038</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>232</v>
@@ -21773,26 +21843,26 @@
       <c r="H118" s="7"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="12" t="s">
+      <c r="A119" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C119" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E119" s="12"/>
-      <c r="F119" s="12" t="n">
+      <c r="C119" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G119" s="12" t="s">
-        <v>1028</v>
-      </c>
-      <c r="H119" s="12"/>
+      <c r="G119" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H119" s="13"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
@@ -21835,48 +21905,48 @@
       <c r="H121" s="7"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C122" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E122" s="12"/>
-      <c r="F122" s="12" t="n">
+      <c r="C122" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="12" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H122" s="12"/>
+      <c r="G122" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H122" s="13"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="12" t="s">
+      <c r="A123" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C123" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E123" s="12"/>
-      <c r="F123" s="12" t="n">
+      <c r="C123" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G123" s="12" t="s">
-        <v>1030</v>
-      </c>
-      <c r="H123" s="12"/>
+      <c r="G123" s="13" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H123" s="13"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
@@ -21923,7 +21993,7 @@
         <v>87</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>232</v>
@@ -21943,7 +22013,7 @@
         <v>87</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>232</v>
@@ -21959,33 +22029,33 @@
       <c r="H127" s="7"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E128" s="12"/>
-      <c r="F128" s="12" t="n">
+      <c r="C128" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E128" s="13"/>
+      <c r="F128" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G128" s="12" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H128" s="12"/>
+      <c r="G128" s="13" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H128" s="13"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
         <v>87</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>232</v>
@@ -22014,7 +22084,7 @@
         <v>226</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="F130" s="7" t="n">
         <v>0</v>
@@ -22023,26 +22093,26 @@
       <c r="H130" s="7"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="12" t="s">
+      <c r="A131" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B131" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E131" s="12"/>
-      <c r="F131" s="12" t="n">
+      <c r="C131" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E131" s="13"/>
+      <c r="F131" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G131" s="12" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H131" s="12"/>
+      <c r="G131" s="13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H131" s="13"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
@@ -22105,26 +22175,26 @@
       <c r="H134" s="7"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="12" t="s">
+      <c r="A135" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C135" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E135" s="12"/>
-      <c r="F135" s="12" t="n">
+      <c r="C135" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E135" s="13"/>
+      <c r="F135" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G135" s="12" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H135" s="12"/>
+      <c r="G135" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H135" s="13"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
@@ -22171,7 +22241,7 @@
         <v>121</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>232</v>
@@ -22187,26 +22257,26 @@
       <c r="H138" s="7"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="12" t="s">
+      <c r="A139" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="D139" s="12" t="s">
+      <c r="D139" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E139" s="12"/>
-      <c r="F139" s="12" t="n">
+      <c r="E139" s="13"/>
+      <c r="F139" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G139" s="12" t="s">
-        <v>1038</v>
-      </c>
-      <c r="H139" s="12"/>
+      <c r="G139" s="13" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H139" s="13"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
@@ -22269,26 +22339,26 @@
       <c r="H142" s="7"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="12" t="s">
+      <c r="A143" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="B143" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C143" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D143" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E143" s="12"/>
-      <c r="F143" s="12" t="n">
+      <c r="C143" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E143" s="13"/>
+      <c r="F143" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G143" s="12" t="s">
-        <v>1039</v>
-      </c>
-      <c r="H143" s="12"/>
+      <c r="G143" s="13" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H143" s="13"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
@@ -22301,7 +22371,7 @@
         <v>405</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E144" s="7"/>
       <c r="F144" s="7" t="n">
@@ -22315,13 +22385,13 @@
         <v>121</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E145" s="7"/>
       <c r="F145" s="7" t="n">
@@ -22341,7 +22411,7 @@
         <v>405</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="n">
@@ -22351,39 +22421,39 @@
       <c r="H146" s="7"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="12" t="s">
+      <c r="A147" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B147" s="12" t="s">
+      <c r="B147" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C147" s="12" t="s">
+      <c r="C147" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D147" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E147" s="12"/>
-      <c r="F147" s="12" t="n">
+      <c r="D147" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G147" s="12" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H147" s="12"/>
+      <c r="G147" s="13" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H147" s="13"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E148" s="7"/>
       <c r="F148" s="7" t="n">
@@ -22403,7 +22473,7 @@
         <v>405</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="n">
@@ -22423,7 +22493,7 @@
         <v>405</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E150" s="7"/>
       <c r="F150" s="7" t="n">
@@ -22443,7 +22513,7 @@
         <v>405</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E151" s="7"/>
       <c r="F151" s="7" t="n">
@@ -22463,7 +22533,7 @@
         <v>405</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E152" s="7"/>
       <c r="F152" s="7" t="n">
@@ -22483,7 +22553,7 @@
         <v>405</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E153" s="7"/>
       <c r="F153" s="7" t="n">
@@ -22497,13 +22567,13 @@
         <v>121</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E154" s="7"/>
       <c r="F154" s="7" t="n">
@@ -22517,13 +22587,13 @@
         <v>121</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E155" s="7"/>
       <c r="F155" s="7" t="n">
@@ -22543,7 +22613,7 @@
         <v>405</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E156" s="7"/>
       <c r="F156" s="7" t="n">
@@ -22553,26 +22623,26 @@
       <c r="H156" s="7"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="12" t="s">
+      <c r="A157" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B157" s="12" t="s">
+      <c r="B157" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C157" s="12" t="s">
+      <c r="C157" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D157" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E157" s="12"/>
-      <c r="F157" s="12" t="n">
+      <c r="D157" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E157" s="13"/>
+      <c r="F157" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G157" s="12" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H157" s="12"/>
+      <c r="G157" s="13" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H157" s="13"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
@@ -22585,7 +22655,7 @@
         <v>405</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E158" s="7"/>
       <c r="F158" s="7" t="n">
@@ -22605,7 +22675,7 @@
         <v>405</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E159" s="7"/>
       <c r="F159" s="7" t="n">
@@ -22625,7 +22695,7 @@
         <v>405</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E160" s="7"/>
       <c r="F160" s="7" t="n">
@@ -22645,7 +22715,7 @@
         <v>405</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E161" s="7"/>
       <c r="F161" s="7" t="n">
@@ -22665,7 +22735,7 @@
         <v>405</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E162" s="7"/>
       <c r="F162" s="7" t="n">
@@ -22685,7 +22755,7 @@
         <v>405</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E163" s="7"/>
       <c r="F163" s="7" t="n">
@@ -22705,7 +22775,7 @@
         <v>405</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E164" s="7"/>
       <c r="F164" s="7" t="n">
@@ -22725,7 +22795,7 @@
         <v>405</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E165" s="7"/>
       <c r="F165" s="7" t="n">
@@ -22745,7 +22815,7 @@
         <v>405</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E166" s="7"/>
       <c r="F166" s="7" t="n">
@@ -22765,7 +22835,7 @@
         <v>405</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="7" t="n">
@@ -22799,7 +22869,7 @@
         <v>121</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>232</v>
@@ -22835,33 +22905,33 @@
       <c r="H170" s="7"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="12" t="s">
+      <c r="A171" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B171" s="12" t="s">
+      <c r="B171" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C171" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E171" s="12"/>
-      <c r="F171" s="12" t="n">
+      <c r="C171" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E171" s="13"/>
+      <c r="F171" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G171" s="12" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H171" s="12"/>
+      <c r="G171" s="13" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H171" s="13"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>232</v>
@@ -22937,33 +23007,33 @@
       <c r="H175" s="7"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C176" s="12" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E176" s="12"/>
-      <c r="F176" s="12" t="n">
+      <c r="C176" s="13" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E176" s="13"/>
+      <c r="F176" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G176" s="12" t="s">
-        <v>1048</v>
-      </c>
-      <c r="H176" s="12"/>
+      <c r="G176" s="13" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H176" s="13"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="C177" s="7" t="s">
         <v>232</v>
@@ -22983,7 +23053,7 @@
         <v>121</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>232</v>
@@ -23039,33 +23109,33 @@
       <c r="H180" s="7"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="12" t="s">
+      <c r="A181" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B181" s="12" t="s">
+      <c r="B181" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C181" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D181" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E181" s="12"/>
-      <c r="F181" s="12" t="n">
+      <c r="C181" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E181" s="13"/>
+      <c r="F181" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G181" s="12" t="s">
-        <v>1049</v>
-      </c>
-      <c r="H181" s="12"/>
+      <c r="G181" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H181" s="13"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>232</v>
@@ -23085,10 +23155,10 @@
         <v>121</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="D183" s="7" t="s">
         <v>233</v>
@@ -23105,7 +23175,7 @@
         <v>121</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>232</v>
@@ -23125,7 +23195,7 @@
         <v>121</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="C185" s="7" t="s">
         <v>232</v>
@@ -23205,7 +23275,7 @@
         <v>121</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>232</v>
@@ -23221,48 +23291,48 @@
       <c r="H189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="12" t="s">
+      <c r="A190" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B190" s="12" t="s">
+      <c r="B190" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C190" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E190" s="12"/>
-      <c r="F190" s="12" t="n">
+      <c r="C190" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E190" s="13"/>
+      <c r="F190" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G190" s="12" t="s">
-        <v>1054</v>
-      </c>
-      <c r="H190" s="12"/>
+      <c r="G190" s="13" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H190" s="13"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="12" t="s">
+      <c r="A191" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B191" s="12" t="s">
+      <c r="B191" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C191" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D191" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E191" s="12"/>
-      <c r="F191" s="12" t="n">
+      <c r="C191" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E191" s="13"/>
+      <c r="F191" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G191" s="12" t="s">
-        <v>1055</v>
-      </c>
-      <c r="H191" s="12"/>
+      <c r="G191" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H191" s="13"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
@@ -23312,7 +23382,7 @@
         <v>442</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="D194" s="7" t="s">
         <v>233</v>
@@ -23325,26 +23395,26 @@
       <c r="H194" s="7"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="12" t="s">
+      <c r="A195" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B195" s="12" t="s">
+      <c r="B195" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C195" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D195" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E195" s="12"/>
-      <c r="F195" s="12" t="n">
+      <c r="C195" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E195" s="13"/>
+      <c r="F195" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G195" s="12" t="s">
-        <v>1056</v>
-      </c>
-      <c r="H195" s="12"/>
+      <c r="G195" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H195" s="13"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
@@ -23387,26 +23457,26 @@
       <c r="H197" s="7"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="12" t="s">
+      <c r="A198" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B198" s="12" t="s">
+      <c r="B198" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C198" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D198" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E198" s="12"/>
-      <c r="F198" s="12" t="n">
+      <c r="C198" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E198" s="13"/>
+      <c r="F198" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G198" s="12" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H198" s="12"/>
+      <c r="G198" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H198" s="13"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
@@ -23453,7 +23523,7 @@
         <v>121</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>232</v>
@@ -23473,7 +23543,7 @@
         <v>121</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>232</v>
@@ -23493,7 +23563,7 @@
         <v>121</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="C203" s="7" t="s">
         <v>232</v>
@@ -23519,10 +23589,10 @@
         <v>405</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="F204" s="7" t="n">
         <v>0</v>
@@ -23541,10 +23611,10 @@
         <v>405</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="F205" s="7" t="n">
         <v>0</v>
@@ -23553,27 +23623,27 @@
       <c r="H205" s="7"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B206" s="11" t="s">
+      <c r="A206" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B206" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C206" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D206" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E206" s="11" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F206" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" s="11"/>
-      <c r="H206" s="11" t="s">
-        <v>960</v>
+      <c r="C206" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F206" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" s="12"/>
+      <c r="H206" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23587,10 +23657,10 @@
         <v>405</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="F207" s="7" t="n">
         <v>0</v>
@@ -23609,10 +23679,10 @@
         <v>405</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="F208" s="7" t="n">
         <v>0</v>
@@ -23621,27 +23691,27 @@
       <c r="H208" s="7"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B209" s="11" t="s">
+      <c r="A209" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B209" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C209" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D209" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E209" s="11" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F209" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" s="11"/>
-      <c r="H209" s="11" t="s">
-        <v>960</v>
+      <c r="C209" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F209" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="12"/>
+      <c r="H209" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23655,10 +23725,10 @@
         <v>405</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="F210" s="7" t="n">
         <v>0</v>
@@ -23677,10 +23747,10 @@
         <v>405</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F211" s="7" t="n">
         <v>0</v>
@@ -23699,10 +23769,10 @@
         <v>405</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F212" s="7" t="n">
         <v>0</v>
@@ -23721,10 +23791,10 @@
         <v>405</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F213" s="7" t="n">
         <v>0</v>
@@ -23733,28 +23803,28 @@
       <c r="H213" s="7"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B214" s="12" t="s">
+      <c r="A214" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B214" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C214" s="12" t="s">
+      <c r="C214" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D214" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E214" s="12" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F214" s="12" t="n">
+      <c r="D214" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F214" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G214" s="12" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H214" s="12"/>
+      <c r="G214" s="13" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H214" s="13"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
@@ -23767,10 +23837,10 @@
         <v>405</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F215" s="7" t="n">
         <v>0</v>
@@ -23789,10 +23859,10 @@
         <v>405</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F216" s="7" t="n">
         <v>0</v>
@@ -23805,16 +23875,16 @@
         <v>54</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F217" s="7" t="n">
         <v>0</v>
@@ -23836,7 +23906,7 @@
         <v>226</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="F218" s="7" t="n">
         <v>0</v>
@@ -23855,10 +23925,10 @@
         <v>405</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F219" s="7" t="n">
         <v>0</v>
@@ -23877,10 +23947,10 @@
         <v>405</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F220" s="7" t="n">
         <v>0</v>
@@ -23899,10 +23969,10 @@
         <v>405</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F221" s="7" t="n">
         <v>0</v>
@@ -23921,10 +23991,10 @@
         <v>405</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F222" s="7" t="n">
         <v>0</v>
@@ -23943,10 +24013,10 @@
         <v>405</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F223" s="7" t="n">
         <v>0</v>
@@ -23959,16 +24029,16 @@
         <v>54</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>1062</v>
+        <v>1073</v>
       </c>
       <c r="C224" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="F224" s="7" t="n">
         <v>0</v>
@@ -23981,16 +24051,16 @@
         <v>54</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="F225" s="7" t="n">
         <v>0</v>
@@ -24003,16 +24073,16 @@
         <v>54</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="C226" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E226" s="7" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F226" s="7" t="n">
         <v>0</v>
@@ -24031,7 +24101,7 @@
         <v>405</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="7" t="n">
@@ -24051,7 +24121,7 @@
         <v>405</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7" t="n">
@@ -24071,7 +24141,7 @@
         <v>405</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7" t="n">
@@ -24091,7 +24161,7 @@
         <v>405</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7" t="n">
@@ -24111,7 +24181,7 @@
         <v>405</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7" t="n">
@@ -24131,7 +24201,7 @@
         <v>405</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7" t="n">
@@ -24145,13 +24215,13 @@
         <v>54</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="C233" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7" t="n">
@@ -24165,13 +24235,13 @@
         <v>54</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7" t="n">
@@ -24185,13 +24255,13 @@
         <v>54</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7" t="n">
@@ -24205,13 +24275,13 @@
         <v>54</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7" t="n">
@@ -24231,7 +24301,7 @@
         <v>405</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7" t="n">
@@ -24241,27 +24311,27 @@
       <c r="H237" s="7"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B238" s="11" t="s">
+      <c r="A238" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B238" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C238" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D238" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E238" s="11" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F238" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" s="11"/>
-      <c r="H238" s="11" t="s">
-        <v>960</v>
+      <c r="C238" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D238" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E238" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F238" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" s="12"/>
+      <c r="H238" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24275,7 +24345,7 @@
         <v>226</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7" t="n">
@@ -24295,7 +24365,7 @@
         <v>405</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7" t="n">
@@ -24305,33 +24375,33 @@
       <c r="H240" s="7"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B241" s="12" t="s">
+      <c r="A241" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B241" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C241" s="12" t="s">
+      <c r="C241" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D241" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E241" s="12"/>
-      <c r="F241" s="12" t="n">
+      <c r="D241" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E241" s="13"/>
+      <c r="F241" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G241" s="12" t="s">
-        <v>1072</v>
-      </c>
-      <c r="H241" s="12"/>
+      <c r="G241" s="13" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H241" s="13"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="C242" s="7" t="s">
         <v>232</v>
@@ -24351,13 +24421,13 @@
         <v>54</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="C243" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="7" t="n">
@@ -24371,13 +24441,13 @@
         <v>54</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="C244" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7" t="n">
@@ -24397,7 +24467,7 @@
         <v>405</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E245" s="7"/>
       <c r="F245" s="7" t="n">
@@ -24411,13 +24481,13 @@
         <v>54</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E246" s="7"/>
       <c r="F246" s="7" t="n">
@@ -24437,7 +24507,7 @@
         <v>405</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E247" s="7"/>
       <c r="F247" s="7" t="n">
@@ -24451,13 +24521,13 @@
         <v>54</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D248" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E248" s="7"/>
       <c r="F248" s="7" t="n">
@@ -24471,13 +24541,13 @@
         <v>54</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E249" s="7"/>
       <c r="F249" s="7" t="n">
@@ -24491,13 +24561,13 @@
         <v>54</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D250" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E250" s="7"/>
       <c r="F250" s="7" t="n">
@@ -24511,13 +24581,13 @@
         <v>54</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E251" s="7"/>
       <c r="F251" s="7" t="n">
@@ -24531,13 +24601,13 @@
         <v>54</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D252" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E252" s="7"/>
       <c r="F252" s="7" t="n">
@@ -24551,13 +24621,13 @@
         <v>54</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E253" s="7"/>
       <c r="F253" s="7" t="n">
@@ -24567,39 +24637,39 @@
       <c r="H253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B254" s="12" t="s">
+      <c r="A254" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B254" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C254" s="12" t="s">
+      <c r="C254" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D254" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E254" s="12"/>
-      <c r="F254" s="12" t="n">
+      <c r="D254" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E254" s="13"/>
+      <c r="F254" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G254" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H254" s="12"/>
+      <c r="G254" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H254" s="13"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D255" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E255" s="7"/>
       <c r="F255" s="7" t="n">
@@ -24619,7 +24689,7 @@
         <v>405</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7" t="n">
@@ -24633,13 +24703,13 @@
         <v>54</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="C257" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D257" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E257" s="7"/>
       <c r="F257" s="7" t="n">
@@ -24659,7 +24729,7 @@
         <v>405</v>
       </c>
       <c r="D258" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="7" t="n">
@@ -24679,7 +24749,7 @@
         <v>405</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="7" t="n">
@@ -24699,7 +24769,7 @@
         <v>405</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E260" s="7"/>
       <c r="F260" s="7" t="n">
@@ -24719,7 +24789,7 @@
         <v>405</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="7" t="n">
@@ -24733,13 +24803,13 @@
         <v>54</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="C262" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7" t="n">
@@ -24753,13 +24823,13 @@
         <v>54</v>
       </c>
       <c r="B263" s="7" t="s">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="C263" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7" t="n">
@@ -24779,7 +24849,7 @@
         <v>405</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="7" t="n">
@@ -24799,7 +24869,7 @@
         <v>405</v>
       </c>
       <c r="D265" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7" t="n">
@@ -24819,7 +24889,7 @@
         <v>405</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7" t="n">
@@ -24839,7 +24909,7 @@
         <v>405</v>
       </c>
       <c r="D267" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7" t="n">
@@ -24853,13 +24923,13 @@
         <v>54</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>1027</v>
+        <v>1038</v>
       </c>
       <c r="C268" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="7" t="n">
@@ -24879,7 +24949,7 @@
         <v>405</v>
       </c>
       <c r="D269" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7" t="n">
@@ -24899,7 +24969,7 @@
         <v>405</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="7" t="n">
@@ -24919,7 +24989,7 @@
         <v>405</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="7" t="n">
@@ -24939,7 +25009,7 @@
         <v>405</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="7" t="n">
@@ -24959,7 +25029,7 @@
         <v>405</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7" t="n">
@@ -24979,7 +25049,7 @@
         <v>405</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7" t="n">
@@ -24999,7 +25069,7 @@
         <v>405</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7" t="n">
@@ -25019,7 +25089,7 @@
         <v>405</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7" t="n">
@@ -25039,7 +25109,7 @@
         <v>405</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7" t="n">
@@ -25059,7 +25129,7 @@
         <v>405</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7" t="n">
@@ -25079,7 +25149,7 @@
         <v>405</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7" t="n">
@@ -25099,7 +25169,7 @@
         <v>405</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7" t="n">
@@ -25119,7 +25189,7 @@
         <v>405</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7" t="n">
@@ -25139,7 +25209,7 @@
         <v>405</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7" t="n">
@@ -25159,7 +25229,7 @@
         <v>405</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7" t="n">
@@ -25179,7 +25249,7 @@
         <v>405</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7" t="n">
@@ -25199,7 +25269,7 @@
         <v>405</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E285" s="7"/>
       <c r="F285" s="7" t="n">
@@ -25219,7 +25289,7 @@
         <v>405</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7" t="n">
@@ -25229,26 +25299,26 @@
       <c r="H286" s="7"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B287" s="12" t="s">
+      <c r="A287" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B287" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C287" s="12" t="s">
+      <c r="C287" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D287" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E287" s="12"/>
-      <c r="F287" s="12" t="n">
+      <c r="D287" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E287" s="13"/>
+      <c r="F287" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G287" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="H287" s="12"/>
+      <c r="G287" s="13" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H287" s="13"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="7" t="s">
@@ -25261,7 +25331,7 @@
         <v>405</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7" t="n">
@@ -25281,7 +25351,7 @@
         <v>405</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7" t="n">
@@ -25301,7 +25371,7 @@
         <v>405</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7" t="n">
@@ -25324,7 +25394,7 @@
         <v>226</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F291" s="7" t="n">
         <v>0</v>
@@ -25343,7 +25413,7 @@
         <v>405</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7" t="n">
@@ -25383,7 +25453,7 @@
         <v>405</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7" t="n">
@@ -25397,13 +25467,13 @@
         <v>54</v>
       </c>
       <c r="B295" s="7" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="C295" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7" t="n">
@@ -25423,7 +25493,7 @@
         <v>405</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7" t="n">
@@ -25437,13 +25507,13 @@
         <v>54</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="C297" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7" t="n">
@@ -25463,7 +25533,7 @@
         <v>405</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7" t="n">
@@ -25483,7 +25553,7 @@
         <v>405</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7" t="n">
@@ -25503,7 +25573,7 @@
         <v>405</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7" t="n">
@@ -25517,13 +25587,13 @@
         <v>54</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="C301" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7" t="n">
@@ -25533,39 +25603,39 @@
       <c r="H301" s="7"/>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B302" s="12" t="s">
+      <c r="A302" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B302" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C302" s="12" t="s">
+      <c r="C302" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D302" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E302" s="12"/>
-      <c r="F302" s="12" t="n">
+      <c r="D302" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E302" s="13"/>
+      <c r="F302" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G302" s="12" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H302" s="12"/>
+      <c r="G302" s="13" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H302" s="13"/>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>1081</v>
+        <v>1092</v>
       </c>
       <c r="C303" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7" t="n">
@@ -25579,13 +25649,13 @@
         <v>54</v>
       </c>
       <c r="B304" s="7" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="C304" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D304" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7" t="n">
@@ -25599,13 +25669,13 @@
         <v>54</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="C305" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D305" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7" t="n">
@@ -25619,13 +25689,13 @@
         <v>54</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="C306" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7" t="n">
@@ -25639,13 +25709,13 @@
         <v>54</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="C307" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7" t="n">
@@ -25659,13 +25729,13 @@
         <v>54</v>
       </c>
       <c r="B308" s="7" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="C308" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D308" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7" t="n">
@@ -25679,13 +25749,13 @@
         <v>54</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="C309" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7" t="n">
@@ -25699,13 +25769,13 @@
         <v>54</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="C310" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7" t="n">
@@ -25719,13 +25789,13 @@
         <v>54</v>
       </c>
       <c r="B311" s="7" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="C311" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7" t="n">
@@ -25739,13 +25809,13 @@
         <v>54</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="C312" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7" t="n">
@@ -25759,13 +25829,13 @@
         <v>54</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="C313" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D313" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7" t="n">
@@ -25779,13 +25849,13 @@
         <v>54</v>
       </c>
       <c r="B314" s="7" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="C314" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D314" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7" t="n">
@@ -25799,13 +25869,13 @@
         <v>54</v>
       </c>
       <c r="B315" s="7" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="C315" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D315" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E315" s="7"/>
       <c r="F315" s="7" t="n">
@@ -25819,13 +25889,13 @@
         <v>54</v>
       </c>
       <c r="B316" s="7" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="C316" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D316" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7" t="n">
@@ -25839,13 +25909,13 @@
         <v>54</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
       <c r="C317" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7" t="n">
@@ -25855,39 +25925,39 @@
       <c r="H317" s="7"/>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B318" s="12" t="s">
+      <c r="A318" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B318" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C318" s="12" t="s">
+      <c r="C318" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D318" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E318" s="12"/>
-      <c r="F318" s="12" t="n">
+      <c r="D318" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E318" s="13"/>
+      <c r="F318" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G318" s="12" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H318" s="12"/>
+      <c r="G318" s="13" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H318" s="13"/>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="C319" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7" t="n">
@@ -25901,13 +25971,13 @@
         <v>54</v>
       </c>
       <c r="B320" s="7" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="C320" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7" t="n">
@@ -25921,7 +25991,7 @@
         <v>54</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="C321" s="7" t="s">
         <v>232</v>
@@ -25941,13 +26011,13 @@
         <v>54</v>
       </c>
       <c r="B322" s="7" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="C322" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7" t="n">
@@ -25957,33 +26027,33 @@
       <c r="H322" s="7"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B323" s="12" t="s">
+      <c r="A323" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B323" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C323" s="12" t="s">
+      <c r="C323" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D323" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E323" s="12"/>
-      <c r="F323" s="12" t="n">
+      <c r="D323" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E323" s="13"/>
+      <c r="F323" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G323" s="12" t="s">
-        <v>1101</v>
-      </c>
-      <c r="H323" s="12"/>
+      <c r="G323" s="13" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H323" s="13"/>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="C324" s="7" t="s">
         <v>232</v>
@@ -26003,13 +26073,13 @@
         <v>54</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="C325" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="7" t="n">
@@ -26023,7 +26093,7 @@
         <v>54</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>1104</v>
+        <v>1115</v>
       </c>
       <c r="C326" s="7" t="s">
         <v>232</v>
@@ -26043,13 +26113,13 @@
         <v>54</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="C327" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E327" s="7"/>
       <c r="F327" s="7" t="n">
@@ -26059,39 +26129,39 @@
       <c r="H327" s="7"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B328" s="12" t="s">
+      <c r="A328" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B328" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C328" s="12" t="s">
+      <c r="C328" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D328" s="12" t="s">
-        <v>956</v>
-      </c>
-      <c r="E328" s="12"/>
-      <c r="F328" s="12" t="n">
+      <c r="D328" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="E328" s="13"/>
+      <c r="F328" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G328" s="12" t="s">
-        <v>1106</v>
-      </c>
-      <c r="H328" s="12"/>
+      <c r="G328" s="13" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H328" s="13"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="C329" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D329" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E329" s="7"/>
       <c r="F329" s="7" t="n">
@@ -26105,13 +26175,13 @@
         <v>54</v>
       </c>
       <c r="B330" s="7" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C330" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D330" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="7" t="n">
@@ -26125,13 +26195,13 @@
         <v>54</v>
       </c>
       <c r="B331" s="7" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="C331" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D331" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E331" s="7"/>
       <c r="F331" s="7" t="n">
@@ -26145,13 +26215,13 @@
         <v>54</v>
       </c>
       <c r="B332" s="7" t="s">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="C332" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D332" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E332" s="7"/>
       <c r="F332" s="7" t="n">
@@ -26165,13 +26235,13 @@
         <v>54</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="C333" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D333" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E333" s="7"/>
       <c r="F333" s="7" t="n">
@@ -26185,13 +26255,13 @@
         <v>54</v>
       </c>
       <c r="B334" s="7" t="s">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="C334" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D334" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7" t="n">
@@ -26205,13 +26275,13 @@
         <v>54</v>
       </c>
       <c r="B335" s="7" t="s">
-        <v>1113</v>
+        <v>1124</v>
       </c>
       <c r="C335" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D335" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7" t="n">
@@ -26225,13 +26295,13 @@
         <v>54</v>
       </c>
       <c r="B336" s="7" t="s">
-        <v>1114</v>
+        <v>1125</v>
       </c>
       <c r="C336" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7" t="n">
@@ -26245,13 +26315,13 @@
         <v>54</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>1115</v>
+        <v>1126</v>
       </c>
       <c r="C337" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7" t="n">
@@ -26261,27 +26331,27 @@
       <c r="H337" s="7"/>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B338" s="11" t="s">
+      <c r="A338" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B338" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C338" s="11" t="s">
-        <v>957</v>
-      </c>
-      <c r="D338" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E338" s="11" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F338" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G338" s="11"/>
-      <c r="H338" s="11" t="s">
-        <v>960</v>
+      <c r="C338" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="D338" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="E338" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F338" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" s="12"/>
+      <c r="H338" s="12" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26289,13 +26359,13 @@
         <v>54</v>
       </c>
       <c r="B339" s="7" t="s">
-        <v>1116</v>
+        <v>1127</v>
       </c>
       <c r="C339" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E339" s="7"/>
       <c r="F339" s="7" t="n">
@@ -26309,13 +26379,13 @@
         <v>54</v>
       </c>
       <c r="B340" s="7" t="s">
-        <v>1117</v>
+        <v>1128</v>
       </c>
       <c r="C340" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7" t="n">
@@ -26329,7 +26399,7 @@
         <v>54</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>1118</v>
+        <v>1129</v>
       </c>
       <c r="C341" s="7" t="s">
         <v>232</v>
@@ -26349,13 +26419,13 @@
         <v>54</v>
       </c>
       <c r="B342" s="7" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="C342" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7" t="n">
@@ -26369,13 +26439,13 @@
         <v>54</v>
       </c>
       <c r="B343" s="7" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="C343" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D343" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7" t="n">
@@ -26389,13 +26459,13 @@
         <v>54</v>
       </c>
       <c r="B344" s="7" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="C344" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D344" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7" t="n">
@@ -26409,13 +26479,13 @@
         <v>54</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="C345" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D345" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7" t="n">
@@ -26429,13 +26499,13 @@
         <v>54</v>
       </c>
       <c r="B346" s="7" t="s">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="C346" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D346" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7" t="n">
@@ -26449,13 +26519,13 @@
         <v>54</v>
       </c>
       <c r="B347" s="7" t="s">
-        <v>1124</v>
+        <v>1135</v>
       </c>
       <c r="C347" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D347" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7" t="n">
@@ -26469,13 +26539,13 @@
         <v>54</v>
       </c>
       <c r="B348" s="7" t="s">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="C348" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D348" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7" t="n">
@@ -26489,13 +26559,13 @@
         <v>54</v>
       </c>
       <c r="B349" s="7" t="s">
-        <v>1126</v>
+        <v>1137</v>
       </c>
       <c r="C349" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D349" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7" t="n">
@@ -26509,13 +26579,13 @@
         <v>54</v>
       </c>
       <c r="B350" s="7" t="s">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="C350" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D350" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7" t="n">
@@ -26529,13 +26599,13 @@
         <v>54</v>
       </c>
       <c r="B351" s="7" t="s">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="C351" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D351" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7" t="n">
@@ -26549,13 +26619,13 @@
         <v>54</v>
       </c>
       <c r="B352" s="7" t="s">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="C352" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D352" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7" t="n">
@@ -26569,13 +26639,13 @@
         <v>54</v>
       </c>
       <c r="B353" s="7" t="s">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="C353" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D353" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7" t="n">
@@ -26589,13 +26659,13 @@
         <v>54</v>
       </c>
       <c r="B354" s="7" t="s">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="C354" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D354" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7" t="n">
@@ -26609,13 +26679,13 @@
         <v>54</v>
       </c>
       <c r="B355" s="7" t="s">
-        <v>1132</v>
+        <v>1143</v>
       </c>
       <c r="C355" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D355" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7" t="n">
@@ -26629,13 +26699,13 @@
         <v>54</v>
       </c>
       <c r="B356" s="7" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="C356" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D356" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7" t="n">
@@ -26649,13 +26719,13 @@
         <v>54</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="C357" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D357" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7" t="n">
@@ -26669,7 +26739,7 @@
         <v>54</v>
       </c>
       <c r="B358" s="7" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="C358" s="7" t="s">
         <v>232</v>
@@ -26689,7 +26759,7 @@
         <v>54</v>
       </c>
       <c r="B359" s="7" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="C359" s="7" t="s">
         <v>232</v>
@@ -26709,13 +26779,13 @@
         <v>54</v>
       </c>
       <c r="B360" s="7" t="s">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="C360" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D360" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7" t="n">
@@ -26729,13 +26799,13 @@
         <v>54</v>
       </c>
       <c r="B361" s="7" t="s">
-        <v>1138</v>
+        <v>1149</v>
       </c>
       <c r="C361" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D361" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7" t="n">
@@ -26749,13 +26819,13 @@
         <v>54</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="C362" s="7" t="s">
         <v>405</v>
       </c>
       <c r="D362" s="7" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7" t="n">
@@ -26813,7 +26883,7 @@
         <v>219</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26824,10 +26894,10 @@
         <v>222</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>225</v>
@@ -26836,7 +26906,7 @@
         <v>226</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26850,16 +26920,16 @@
         <v>364</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>233</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26873,16 +26943,16 @@
         <v>364</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>233</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26896,16 +26966,16 @@
         <v>355</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>233</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26919,16 +26989,16 @@
         <v>355</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>233</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26942,16 +27012,16 @@
         <v>355</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>233</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
   </sheetData>
@@ -26980,11 +27050,11 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>1150</v>
+      <c r="A1" s="11" t="s">
+        <v>1161</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26992,8 +27062,8 @@
       <c r="B2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>1152</v>
+      <c r="A3" s="11" t="s">
+        <v>1163</v>
       </c>
       <c r="B3" s="14" t="n">
         <f aca="false">COUNTA('200V Devices'!C2:C393)</f>
@@ -27002,7 +27072,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="B4" s="14" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"Done (pilot)")</f>
@@ -27011,7 +27081,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="B5" s="14" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"To do")</f>
@@ -27020,7 +27090,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">COUNTIF('200V Devices'!J2:J393,"Matched from 200V tab")</f>
@@ -27029,7 +27099,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="B7" s="14" t="n">
         <f aca="false">COUNTA('Not found'!C2:C7)</f>
@@ -27037,8 +27107,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>1157</v>
+      <c r="A8" s="11" t="s">
+        <v>1168</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">B3+B7</f>
@@ -27050,11 +27120,11 @@
       <c r="B9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>1158</v>
+      <c r="B10" s="11" t="s">
+        <v>1169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27107,30 +27177,30 @@
       <c r="B16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>1159</v>
+      <c r="A17" s="11" t="s">
+        <v>1170</v>
       </c>
       <c r="B17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1161</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>1163</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>1164</v>
+      <c r="A21" s="11" t="s">
+        <v>1175</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">COUNTA('Ports without device'!A2:A362)</f>
@@ -27139,7 +27209,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="B22" s="14" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,"&gt;0")</f>
@@ -27148,7 +27218,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>1166</v>
+        <v>1177</v>
       </c>
       <c r="B23" s="14" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,0)</f>
@@ -27157,7 +27227,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>1167</v>
+        <v>1178</v>
       </c>
       <c r="B24" s="14" t="n">
         <f aca="false">COUNTIF('Ports without device'!H2:H362,"Pilot staff outlet*")</f>
@@ -27166,7 +27236,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>1168</v>
+        <v>1179</v>
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">COUNTIF('Ports without device'!C2:C362,"None (tagged only)")</f>
@@ -27175,15 +27245,15 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>1169</v>
+        <v>1180</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>1171</v>
+      <c r="A28" s="11" t="s">
+        <v>1182</v>
       </c>
       <c r="B28" s="14" t="n">
         <f aca="false">COUNT(Review!A5:A93)</f>
@@ -27192,7 +27262,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>1172</v>
+        <v>1183</v>
       </c>
       <c r="B29" s="14" t="n">
         <f aca="false">COUNTA(Review!H5:H93)</f>
@@ -27201,7 +27271,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>1173</v>
+        <v>1184</v>
       </c>
       <c r="B30" s="14" t="n">
         <f aca="false">B28-B29</f>

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">10_F0_68_0C_06_D6</t>
   </si>
   <si>
-    <t xml:space="preserve">Via LT2-1 port 1/1/23 (their 1/1/12), confirmed by LLDP. New VLANs tagged on LT2-1 1/1/23 on 6 Oct 2026</t>
+    <t xml:space="preserve">Via LT2-1 port 1/1/23 (their 1/1/12), confirmed by LLDP</t>
   </si>
   <si>
     <t xml:space="preserve">192.168.122.13</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">10_F0_68_0B_D2_3E</t>
   </si>
   <si>
-    <t xml:space="preserve">Via LT2-1 port 1/1/24 (their 1/1/12), confirmed by LLDP. New VLANs tagged on LT2-1 1/1/24 on 6 Oct 2026</t>
+    <t xml:space="preserve">Via LT2-1 port 1/1/24 (their 1/1/12), confirmed by LLDP</t>
   </si>
   <si>
     <t xml:space="preserve">192.168.122.14</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">10:F0:68:0C:06:E1, 10:F0:68:0C:06:D6</t>
   </si>
   <si>
-    <t xml:space="preserve">Uplink to switch-200V-LT2-2 (LLDP). 22 new VLANs (2000-2953) tagged 6 Oct 2026, ahead of cutover</t>
+    <t xml:space="preserve">Uplink to switch-200V-LT2-2 (LLDP)</t>
   </si>
   <si>
     <t xml:space="preserve">10:F0:68:0B:D2:49, 10:F0:68:0B:D2:3E, AC:B4:80:F1:61:7F</t>
   </si>
   <si>
-    <t xml:space="preserve">Uplink to switch-200V-LT2-3 (LLDP). 22 new VLANs (2000-2953) tagged 6 Oct 2026, ahead of cutover</t>
+    <t xml:space="preserve">Uplink to switch-200V-LT2-3 (LLDP)</t>
   </si>
   <si>
     <t xml:space="preserve">1212,1213,1230,1250,1271,1272,1273,2000,2010,2020,2100,2200,2300,2310,2320,2400,2500,2510,2520,2530,2600,2700,2800,2810,2900,2950,2951,2952,2953</t>

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6083" uniqueCount="1284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6096" uniqueCount="1297">
   <si>
     <t xml:space="preserve">200V migration: items for review</t>
   </si>
@@ -3323,6 +3323,9 @@
     <t xml:space="preserve">Moved to 2700 on 9 Oct (unlisted AV device).</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3J5, device 20:7B:D2:30:98:F3 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:9B</t>
   </si>
   <si>
@@ -3446,6 +3449,9 @@
     <t xml:space="preserve">D8:43:AE:B1:6C:A8</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3G16, device 20:7B:D2:30:98:D6 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">4/1/45</t>
   </si>
   <si>
@@ -3461,18 +3467,30 @@
     <t xml:space="preserve">5/1/11</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3H2, device 20:7B:D2:30:99:09 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:B0</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3I8, device 20:7B:D2:30:98:AF (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:3C</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6F:04</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3I16, device 20:7B:D2:30:98:D2 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">5/1/40</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3H14, device 20:7B:D2:30:98:B1 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">5/1/43</t>
   </si>
   <si>
@@ -3482,15 +3500,30 @@
     <t xml:space="preserve">5/1/47</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V3H21, device 20:7B:D2:30:99:29 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1272,1273,2300,2310,2311,2320,2321</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:06</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V4H22, device 20:7B:D2:30:98:FD (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV outlet 200V4I10, device 20:7B:D2:30:98:EF (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">D8:43:AE:B1:6A:29</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V4J4, device 20:7B:D2:30:98:DB (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV outlet 200V4J14, device 20:7B:D2:30:99:0E (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">00:09:F5:32:D9:F7</t>
   </si>
   <si>
@@ -3515,6 +3548,9 @@
     <t xml:space="preserve">A0:4A:5E:E7:D5:71</t>
   </si>
   <si>
+    <t xml:space="preserve">AV outlet 200V4F5, device 20:7B:D2:30:98:DF (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">D8:43:AE:B1:6D:56</t>
   </si>
   <si>
@@ -3522,6 +3558,9 @@
   </si>
   <si>
     <t xml:space="preserve">38:4B:76:E0:B0:B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV outlet 200V4H2, device 20:7B:D2:30:98:C2 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">F8:25:51:CC:2C:76</t>
@@ -21843,7 +21882,9 @@
         <v>0</v>
       </c>
       <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
+      <c r="H57" s="13" t="s">
+        <v>1091</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
@@ -21903,7 +21944,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>1090</v>
@@ -21934,7 +21975,7 @@
         <v>95</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>495</v>
@@ -21967,7 +22008,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>1080</v>
@@ -21998,7 +22039,7 @@
         <v>95</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>495</v>
@@ -22161,10 +22202,10 @@
         <v>145</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E73" s="13"/>
       <c r="F73" s="13" t="n">
@@ -22181,17 +22222,17 @@
         <v>108</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>1080</v>
@@ -22215,7 +22256,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>1080</v>
@@ -22239,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>1080</v>
@@ -22263,7 +22304,7 @@
         <v>1</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>1080</v>
@@ -22280,7 +22321,7 @@
         <v>1062</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="11" t="n">
@@ -22288,7 +22329,7 @@
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22302,7 +22343,7 @@
         <v>1062</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E79" s="11"/>
       <c r="F79" s="11" t="n">
@@ -22310,7 +22351,7 @@
       </c>
       <c r="G79" s="11"/>
       <c r="H79" s="11" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22324,7 +22365,7 @@
         <v>1062</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="11" t="n">
@@ -22332,7 +22373,7 @@
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22346,7 +22387,7 @@
         <v>1062</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E81" s="11"/>
       <c r="F81" s="11" t="n">
@@ -22354,7 +22395,7 @@
       </c>
       <c r="G81" s="11"/>
       <c r="H81" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22368,7 +22409,7 @@
         <v>1062</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11" t="n">
@@ -22376,7 +22417,7 @@
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22390,7 +22431,7 @@
         <v>1062</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11" t="n">
@@ -22398,7 +22439,7 @@
       </c>
       <c r="G83" s="11"/>
       <c r="H83" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22406,7 +22447,7 @@
         <v>95</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>495</v>
@@ -22432,7 +22473,7 @@
         <v>1062</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="11" t="n">
@@ -22440,7 +22481,7 @@
       </c>
       <c r="G85" s="11"/>
       <c r="H85" s="11" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22454,7 +22495,7 @@
         <v>1062</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="11" t="n">
@@ -22462,7 +22503,7 @@
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="11" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22470,13 +22511,13 @@
         <v>95</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>1062</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E87" s="11"/>
       <c r="F87" s="11" t="n">
@@ -22484,7 +22525,7 @@
       </c>
       <c r="G87" s="11"/>
       <c r="H87" s="11" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22498,7 +22539,7 @@
         <v>1062</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="11" t="n">
@@ -22506,7 +22547,7 @@
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22520,7 +22561,7 @@
         <v>1062</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E89" s="11"/>
       <c r="F89" s="11" t="n">
@@ -22528,7 +22569,7 @@
       </c>
       <c r="G89" s="11"/>
       <c r="H89" s="11" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22542,7 +22583,7 @@
         <v>1062</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="11" t="n">
@@ -22550,7 +22591,7 @@
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="11" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22564,7 +22605,7 @@
         <v>1062</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E91" s="11"/>
       <c r="F91" s="11" t="n">
@@ -22572,7 +22613,7 @@
       </c>
       <c r="G91" s="11"/>
       <c r="H91" s="11" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22586,17 +22627,17 @@
         <v>1062</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22610,7 +22651,7 @@
         <v>1062</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="11" t="n">
@@ -22618,7 +22659,7 @@
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22632,7 +22673,7 @@
         <v>1062</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E94" s="11"/>
       <c r="F94" s="11" t="n">
@@ -22640,7 +22681,7 @@
       </c>
       <c r="G94" s="11"/>
       <c r="H94" s="11" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22654,7 +22695,7 @@
         <v>1062</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E95" s="11"/>
       <c r="F95" s="11" t="n">
@@ -22662,7 +22703,7 @@
       </c>
       <c r="G95" s="11"/>
       <c r="H95" s="11" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22676,7 +22717,7 @@
         <v>1062</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="11" t="n">
@@ -22684,7 +22725,7 @@
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22698,7 +22739,7 @@
         <v>1062</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E97" s="11"/>
       <c r="F97" s="11" t="n">
@@ -22706,7 +22747,7 @@
       </c>
       <c r="G97" s="11"/>
       <c r="H97" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22720,7 +22761,7 @@
         <v>1062</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="11" t="n">
@@ -22728,7 +22769,7 @@
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="11" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22742,7 +22783,7 @@
         <v>1062</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E99" s="11"/>
       <c r="F99" s="11" t="n">
@@ -22750,7 +22791,7 @@
       </c>
       <c r="G99" s="11"/>
       <c r="H99" s="11" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22764,7 +22805,7 @@
         <v>1062</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="11" t="n">
@@ -22772,7 +22813,7 @@
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22840,7 +22881,7 @@
         <v>95</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C104" s="13" t="s">
         <v>495</v>
@@ -22860,7 +22901,7 @@
         <v>95</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C105" s="13" t="s">
         <v>495</v>
@@ -22893,7 +22934,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H106" s="11" t="s">
         <v>1080</v>
@@ -22907,17 +22948,17 @@
         <v>121</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E107" s="11"/>
       <c r="F107" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H107" s="11" t="s">
         <v>1080</v>
@@ -22941,7 +22982,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="11" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>1090</v>
@@ -22965,14 +23006,16 @@
         <v>0</v>
       </c>
       <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
+      <c r="H109" s="13" t="s">
+        <v>1133</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="13" t="s">
         <v>95</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C110" s="13" t="s">
         <v>322</v>
@@ -23005,7 +23048,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>1090</v>
@@ -23036,7 +23079,7 @@
         <v>95</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C113" s="13" t="s">
         <v>322</v>
@@ -23056,7 +23099,7 @@
         <v>95</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C114" s="13" t="s">
         <v>322</v>
@@ -23096,7 +23139,7 @@
         <v>95</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C116" s="13" t="s">
         <v>322</v>
@@ -23109,7 +23152,9 @@
         <v>0</v>
       </c>
       <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
+      <c r="H116" s="13" t="s">
+        <v>1139</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="13" t="s">
@@ -23169,7 +23214,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="H119" s="11" t="s">
         <v>1090</v>
@@ -23213,7 +23258,9 @@
         <v>0</v>
       </c>
       <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
+      <c r="H121" s="13" t="s">
+        <v>1141</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="11" t="s">
@@ -23233,7 +23280,7 @@
         <v>1</v>
       </c>
       <c r="G122" s="11" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="H122" s="11" t="s">
         <v>1090</v>
@@ -23257,7 +23304,7 @@
         <v>1</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>1090</v>
@@ -23281,7 +23328,9 @@
         <v>0</v>
       </c>
       <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
+      <c r="H124" s="13" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="13" t="s">
@@ -23308,7 +23357,7 @@
         <v>95</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="C126" s="13" t="s">
         <v>322</v>
@@ -23321,14 +23370,16 @@
         <v>0</v>
       </c>
       <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
+      <c r="H126" s="13" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="13" t="s">
         <v>95</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C127" s="13" t="s">
         <v>322</v>
@@ -23361,7 +23412,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="H128" s="11" t="s">
         <v>1090</v>
@@ -23372,7 +23423,7 @@
         <v>95</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="C129" s="13" t="s">
         <v>322</v>
@@ -23385,7 +23436,9 @@
         <v>0</v>
       </c>
       <c r="G129" s="13"/>
-      <c r="H129" s="13"/>
+      <c r="H129" s="13" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="13" t="s">
@@ -23401,7 +23454,7 @@
         <v>317</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>0</v>
@@ -23427,7 +23480,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="H131" s="11" t="s">
         <v>1090</v>
@@ -23451,7 +23504,9 @@
         <v>0</v>
       </c>
       <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
+      <c r="H132" s="13" t="s">
+        <v>1153</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="13" t="s">
@@ -23491,7 +23546,9 @@
         <v>0</v>
       </c>
       <c r="G134" s="13"/>
-      <c r="H134" s="13"/>
+      <c r="H134" s="13" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="11" t="s">
@@ -23511,7 +23568,7 @@
         <v>1</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="H135" s="11" t="s">
         <v>1090</v>
@@ -23535,7 +23592,9 @@
         <v>0</v>
       </c>
       <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
+      <c r="H136" s="13" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="13" t="s">
@@ -23575,7 +23634,9 @@
         <v>0</v>
       </c>
       <c r="G138" s="13"/>
-      <c r="H138" s="13"/>
+      <c r="H138" s="13" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="17" t="s">
@@ -23595,7 +23656,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="H139" s="17"/>
     </row>
@@ -23677,7 +23738,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="H143" s="11" t="s">
         <v>1090</v>
@@ -23708,7 +23769,7 @@
         <v>135</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="C145" s="13" t="s">
         <v>495</v>
@@ -23761,7 +23822,7 @@
         <v>1</v>
       </c>
       <c r="G147" s="11" t="s">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="H147" s="11" t="s">
         <v>1080</v>
@@ -23772,7 +23833,7 @@
         <v>135</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="C148" s="13" t="s">
         <v>495</v>
@@ -23892,7 +23953,7 @@
         <v>135</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="C154" s="13" t="s">
         <v>495</v>
@@ -23912,7 +23973,7 @@
         <v>135</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="C155" s="13" t="s">
         <v>495</v>
@@ -23965,7 +24026,7 @@
         <v>1</v>
       </c>
       <c r="G157" s="11" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="H157" s="11" t="s">
         <v>1080</v>
@@ -24196,7 +24257,7 @@
         <v>135</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C169" s="13" t="s">
         <v>322</v>
@@ -24229,7 +24290,9 @@
         <v>0</v>
       </c>
       <c r="G170" s="13"/>
-      <c r="H170" s="13"/>
+      <c r="H170" s="13" t="s">
+        <v>1166</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="11" t="s">
@@ -24249,7 +24312,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="11" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="H171" s="11" t="s">
         <v>1090</v>
@@ -24260,7 +24323,7 @@
         <v>135</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C172" s="13" t="s">
         <v>322</v>
@@ -24343,7 +24406,7 @@
         <v>149</v>
       </c>
       <c r="C176" s="17" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="D176" s="17" t="s">
         <v>323</v>
@@ -24353,7 +24416,7 @@
         <v>1</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="H176" s="17"/>
     </row>
@@ -24362,7 +24425,7 @@
         <v>135</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C177" s="13" t="s">
         <v>322</v>
@@ -24375,14 +24438,16 @@
         <v>0</v>
       </c>
       <c r="G177" s="13"/>
-      <c r="H177" s="13"/>
+      <c r="H177" s="13" t="s">
+        <v>1170</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="13" t="s">
         <v>135</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C178" s="13" t="s">
         <v>322</v>
@@ -24455,7 +24520,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="H181" s="17"/>
     </row>
@@ -24464,7 +24529,7 @@
         <v>135</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="C182" s="13" t="s">
         <v>322</v>
@@ -24484,10 +24549,10 @@
         <v>135</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="C183" s="13" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="D183" s="13" t="s">
         <v>323</v>
@@ -24504,7 +24569,7 @@
         <v>135</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="C184" s="13" t="s">
         <v>322</v>
@@ -24524,7 +24589,7 @@
         <v>135</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="C185" s="13" t="s">
         <v>322</v>
@@ -24604,7 +24669,7 @@
         <v>135</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C189" s="13" t="s">
         <v>322</v>
@@ -24637,7 +24702,7 @@
         <v>1</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
       <c r="H190" s="11" t="s">
         <v>1090</v>
@@ -24661,7 +24726,7 @@
         <v>1</v>
       </c>
       <c r="G191" s="11" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="H191" s="11" t="s">
         <v>1090</v>
@@ -24715,7 +24780,7 @@
         <v>532</v>
       </c>
       <c r="C194" s="13" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="D194" s="13" t="s">
         <v>323</v>
@@ -24745,7 +24810,7 @@
         <v>1</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="H195" s="11" t="s">
         <v>1090</v>
@@ -24809,7 +24874,7 @@
         <v>1</v>
       </c>
       <c r="G198" s="11" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="H198" s="11" t="s">
         <v>1090</v>
@@ -24860,7 +24925,7 @@
         <v>135</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="C201" s="13" t="s">
         <v>322</v>
@@ -24880,7 +24945,7 @@
         <v>135</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C202" s="13" t="s">
         <v>322</v>
@@ -24900,7 +24965,7 @@
         <v>135</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="C203" s="13" t="s">
         <v>322</v>
@@ -24929,7 +24994,7 @@
         <v>1062</v>
       </c>
       <c r="E204" s="13" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F204" s="13" t="n">
         <v>0</v>
@@ -24951,7 +25016,7 @@
         <v>1062</v>
       </c>
       <c r="E205" s="13" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F205" s="13" t="n">
         <v>0</v>
@@ -24973,7 +25038,7 @@
         <v>1064</v>
       </c>
       <c r="E206" s="16" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="F206" s="16" t="n">
         <v>0</v>
@@ -24997,7 +25062,7 @@
         <v>1062</v>
       </c>
       <c r="E207" s="13" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F207" s="13" t="n">
         <v>0</v>
@@ -25019,7 +25084,7 @@
         <v>1062</v>
       </c>
       <c r="E208" s="13" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F208" s="13" t="n">
         <v>0</v>
@@ -25041,7 +25106,7 @@
         <v>1064</v>
       </c>
       <c r="E209" s="16" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F209" s="16" t="n">
         <v>0</v>
@@ -25065,7 +25130,7 @@
         <v>1062</v>
       </c>
       <c r="E210" s="13" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F210" s="13" t="n">
         <v>0</v>
@@ -25087,7 +25152,7 @@
         <v>1062</v>
       </c>
       <c r="E211" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F211" s="13" t="n">
         <v>0</v>
@@ -25109,7 +25174,7 @@
         <v>1062</v>
       </c>
       <c r="E212" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F212" s="13" t="n">
         <v>0</v>
@@ -25131,7 +25196,7 @@
         <v>1062</v>
       </c>
       <c r="E213" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F213" s="13" t="n">
         <v>0</v>
@@ -25153,13 +25218,13 @@
         <v>1062</v>
       </c>
       <c r="E214" s="11" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F214" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G214" s="11" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="H214" s="11" t="s">
         <v>1080</v>
@@ -25179,7 +25244,7 @@
         <v>1062</v>
       </c>
       <c r="E215" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F215" s="13" t="n">
         <v>0</v>
@@ -25201,7 +25266,7 @@
         <v>1062</v>
       </c>
       <c r="E216" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F216" s="13" t="n">
         <v>0</v>
@@ -25223,7 +25288,7 @@
         <v>1062</v>
       </c>
       <c r="E217" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F217" s="13" t="n">
         <v>0</v>
@@ -25267,7 +25332,7 @@
         <v>1062</v>
       </c>
       <c r="E219" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F219" s="13" t="n">
         <v>0</v>
@@ -25289,7 +25354,7 @@
         <v>1062</v>
       </c>
       <c r="E220" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F220" s="13" t="n">
         <v>0</v>
@@ -25311,7 +25376,7 @@
         <v>1062</v>
       </c>
       <c r="E221" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F221" s="13" t="n">
         <v>0</v>
@@ -25333,7 +25398,7 @@
         <v>1062</v>
       </c>
       <c r="E222" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F222" s="13" t="n">
         <v>0</v>
@@ -25355,7 +25420,7 @@
         <v>1062</v>
       </c>
       <c r="E223" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F223" s="13" t="n">
         <v>0</v>
@@ -25368,7 +25433,7 @@
         <v>59</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="C224" s="13" t="s">
         <v>495</v>
@@ -25377,7 +25442,7 @@
         <v>1062</v>
       </c>
       <c r="E224" s="13" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="F224" s="13" t="n">
         <v>0</v>
@@ -25390,7 +25455,7 @@
         <v>59</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="C225" s="13" t="s">
         <v>495</v>
@@ -25399,7 +25464,7 @@
         <v>1062</v>
       </c>
       <c r="E225" s="13" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="F225" s="13" t="n">
         <v>0</v>
@@ -25412,7 +25477,7 @@
         <v>59</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="C226" s="13" t="s">
         <v>495</v>
@@ -25421,7 +25486,7 @@
         <v>1062</v>
       </c>
       <c r="E226" s="13" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
       <c r="F226" s="13" t="n">
         <v>0</v>
@@ -25554,7 +25619,7 @@
         <v>59</v>
       </c>
       <c r="B233" s="13" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="C233" s="13" t="s">
         <v>495</v>
@@ -25574,7 +25639,7 @@
         <v>59</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>495</v>
@@ -25594,7 +25659,7 @@
         <v>59</v>
       </c>
       <c r="B235" s="13" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="C235" s="13" t="s">
         <v>495</v>
@@ -25614,7 +25679,7 @@
         <v>59</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="C236" s="13" t="s">
         <v>495</v>
@@ -25663,7 +25728,7 @@
         <v>1064</v>
       </c>
       <c r="E238" s="16" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="F238" s="16" t="n">
         <v>0</v>
@@ -25684,7 +25749,7 @@
         <v>317</v>
       </c>
       <c r="D239" s="13" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="E239" s="13"/>
       <c r="F239" s="13" t="n">
@@ -25731,7 +25796,7 @@
         <v>1</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="H241" s="11" t="s">
         <v>1080</v>
@@ -25742,7 +25807,7 @@
         <v>59</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="C242" s="13" t="s">
         <v>322</v>
@@ -25762,7 +25827,7 @@
         <v>59</v>
       </c>
       <c r="B243" s="13" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C243" s="13" t="s">
         <v>495</v>
@@ -25782,7 +25847,7 @@
         <v>59</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="C244" s="13" t="s">
         <v>495</v>
@@ -25822,7 +25887,7 @@
         <v>59</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="C246" s="13" t="s">
         <v>495</v>
@@ -25862,7 +25927,7 @@
         <v>59</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="C248" s="13" t="s">
         <v>495</v>
@@ -25882,7 +25947,7 @@
         <v>59</v>
       </c>
       <c r="B249" s="13" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="C249" s="13" t="s">
         <v>495</v>
@@ -25902,7 +25967,7 @@
         <v>59</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C250" s="13" t="s">
         <v>495</v>
@@ -25922,7 +25987,7 @@
         <v>59</v>
       </c>
       <c r="B251" s="13" t="s">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="C251" s="13" t="s">
         <v>495</v>
@@ -25942,7 +26007,7 @@
         <v>59</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="C252" s="13" t="s">
         <v>495</v>
@@ -25962,7 +26027,7 @@
         <v>59</v>
       </c>
       <c r="B253" s="13" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="C253" s="13" t="s">
         <v>495</v>
@@ -25995,7 +26060,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="11" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="H254" s="11" t="s">
         <v>1080</v>
@@ -26006,7 +26071,7 @@
         <v>59</v>
       </c>
       <c r="B255" s="13" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C255" s="13" t="s">
         <v>495</v>
@@ -26046,7 +26111,7 @@
         <v>59</v>
       </c>
       <c r="B257" s="13" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C257" s="13" t="s">
         <v>495</v>
@@ -26146,7 +26211,7 @@
         <v>59</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C262" s="13" t="s">
         <v>495</v>
@@ -26166,7 +26231,7 @@
         <v>59</v>
       </c>
       <c r="B263" s="13" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C263" s="13" t="s">
         <v>495</v>
@@ -26266,7 +26331,7 @@
         <v>59</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C268" s="13" t="s">
         <v>495</v>
@@ -26659,7 +26724,7 @@
         <v>1</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="H287" s="11" t="s">
         <v>1080</v>
@@ -26739,7 +26804,7 @@
         <v>317</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="F291" s="13" t="n">
         <v>0</v>
@@ -26812,7 +26877,7 @@
         <v>59</v>
       </c>
       <c r="B295" s="13" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="C295" s="13" t="s">
         <v>495</v>
@@ -26852,7 +26917,7 @@
         <v>59</v>
       </c>
       <c r="B297" s="13" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C297" s="13" t="s">
         <v>495</v>
@@ -26932,7 +26997,7 @@
         <v>59</v>
       </c>
       <c r="B301" s="13" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="C301" s="13" t="s">
         <v>495</v>
@@ -26965,7 +27030,7 @@
         <v>1</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="H302" s="11" t="s">
         <v>1080</v>
@@ -26976,7 +27041,7 @@
         <v>59</v>
       </c>
       <c r="B303" s="13" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="C303" s="13" t="s">
         <v>495</v>
@@ -26996,7 +27061,7 @@
         <v>59</v>
       </c>
       <c r="B304" s="13" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="C304" s="13" t="s">
         <v>495</v>
@@ -27016,7 +27081,7 @@
         <v>59</v>
       </c>
       <c r="B305" s="13" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="C305" s="13" t="s">
         <v>495</v>
@@ -27036,7 +27101,7 @@
         <v>59</v>
       </c>
       <c r="B306" s="13" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="C306" s="13" t="s">
         <v>495</v>
@@ -27056,7 +27121,7 @@
         <v>59</v>
       </c>
       <c r="B307" s="13" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="C307" s="13" t="s">
         <v>495</v>
@@ -27076,7 +27141,7 @@
         <v>59</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="C308" s="13" t="s">
         <v>495</v>
@@ -27096,7 +27161,7 @@
         <v>59</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="C309" s="13" t="s">
         <v>495</v>
@@ -27116,7 +27181,7 @@
         <v>59</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="C310" s="13" t="s">
         <v>495</v>
@@ -27136,7 +27201,7 @@
         <v>59</v>
       </c>
       <c r="B311" s="13" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C311" s="13" t="s">
         <v>495</v>
@@ -27156,7 +27221,7 @@
         <v>59</v>
       </c>
       <c r="B312" s="13" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="C312" s="13" t="s">
         <v>495</v>
@@ -27176,7 +27241,7 @@
         <v>59</v>
       </c>
       <c r="B313" s="13" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="C313" s="13" t="s">
         <v>495</v>
@@ -27196,7 +27261,7 @@
         <v>59</v>
       </c>
       <c r="B314" s="13" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="C314" s="13" t="s">
         <v>495</v>
@@ -27216,7 +27281,7 @@
         <v>59</v>
       </c>
       <c r="B315" s="13" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="C315" s="13" t="s">
         <v>495</v>
@@ -27236,7 +27301,7 @@
         <v>59</v>
       </c>
       <c r="B316" s="13" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="C316" s="13" t="s">
         <v>495</v>
@@ -27256,7 +27321,7 @@
         <v>59</v>
       </c>
       <c r="B317" s="13" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="C317" s="13" t="s">
         <v>495</v>
@@ -27289,7 +27354,7 @@
         <v>1</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="H318" s="11" t="s">
         <v>1080</v>
@@ -27300,7 +27365,7 @@
         <v>59</v>
       </c>
       <c r="B319" s="13" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="C319" s="13" t="s">
         <v>495</v>
@@ -27320,7 +27385,7 @@
         <v>59</v>
       </c>
       <c r="B320" s="13" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="C320" s="13" t="s">
         <v>495</v>
@@ -27340,7 +27405,7 @@
         <v>59</v>
       </c>
       <c r="B321" s="13" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="C321" s="13" t="s">
         <v>322</v>
@@ -27360,7 +27425,7 @@
         <v>59</v>
       </c>
       <c r="B322" s="13" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="C322" s="13" t="s">
         <v>495</v>
@@ -27393,7 +27458,7 @@
         <v>1</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="H323" s="11" t="s">
         <v>1080</v>
@@ -27404,7 +27469,7 @@
         <v>59</v>
       </c>
       <c r="B324" s="13" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="C324" s="13" t="s">
         <v>322</v>
@@ -27424,7 +27489,7 @@
         <v>59</v>
       </c>
       <c r="B325" s="13" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="C325" s="13" t="s">
         <v>495</v>
@@ -27444,7 +27509,7 @@
         <v>59</v>
       </c>
       <c r="B326" s="13" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="C326" s="13" t="s">
         <v>322</v>
@@ -27464,7 +27529,7 @@
         <v>59</v>
       </c>
       <c r="B327" s="13" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="C327" s="13" t="s">
         <v>495</v>
@@ -27497,7 +27562,7 @@
         <v>1</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="H328" s="11" t="s">
         <v>1080</v>
@@ -27508,7 +27573,7 @@
         <v>59</v>
       </c>
       <c r="B329" s="13" t="s">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="C329" s="13" t="s">
         <v>495</v>
@@ -27528,7 +27593,7 @@
         <v>59</v>
       </c>
       <c r="B330" s="13" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="C330" s="13" t="s">
         <v>495</v>
@@ -27548,7 +27613,7 @@
         <v>59</v>
       </c>
       <c r="B331" s="13" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="C331" s="13" t="s">
         <v>495</v>
@@ -27568,7 +27633,7 @@
         <v>59</v>
       </c>
       <c r="B332" s="13" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="C332" s="13" t="s">
         <v>495</v>
@@ -27588,7 +27653,7 @@
         <v>59</v>
       </c>
       <c r="B333" s="13" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="C333" s="13" t="s">
         <v>495</v>
@@ -27608,7 +27673,7 @@
         <v>59</v>
       </c>
       <c r="B334" s="13" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="C334" s="13" t="s">
         <v>495</v>
@@ -27628,7 +27693,7 @@
         <v>59</v>
       </c>
       <c r="B335" s="13" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="C335" s="13" t="s">
         <v>495</v>
@@ -27648,7 +27713,7 @@
         <v>59</v>
       </c>
       <c r="B336" s="13" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="C336" s="13" t="s">
         <v>495</v>
@@ -27668,7 +27733,7 @@
         <v>59</v>
       </c>
       <c r="B337" s="13" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="C337" s="13" t="s">
         <v>495</v>
@@ -27697,7 +27762,7 @@
         <v>1064</v>
       </c>
       <c r="E338" s="16" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="F338" s="16" t="n">
         <v>0</v>
@@ -27712,7 +27777,7 @@
         <v>59</v>
       </c>
       <c r="B339" s="13" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="C339" s="13" t="s">
         <v>495</v>
@@ -27732,7 +27797,7 @@
         <v>59</v>
       </c>
       <c r="B340" s="13" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="C340" s="13" t="s">
         <v>495</v>
@@ -27752,7 +27817,7 @@
         <v>59</v>
       </c>
       <c r="B341" s="13" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="C341" s="13" t="s">
         <v>322</v>
@@ -27772,7 +27837,7 @@
         <v>59</v>
       </c>
       <c r="B342" s="13" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="C342" s="13" t="s">
         <v>495</v>
@@ -27792,7 +27857,7 @@
         <v>59</v>
       </c>
       <c r="B343" s="13" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="C343" s="13" t="s">
         <v>495</v>
@@ -27812,7 +27877,7 @@
         <v>59</v>
       </c>
       <c r="B344" s="13" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="C344" s="13" t="s">
         <v>495</v>
@@ -27832,7 +27897,7 @@
         <v>59</v>
       </c>
       <c r="B345" s="13" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="C345" s="13" t="s">
         <v>495</v>
@@ -27852,7 +27917,7 @@
         <v>59</v>
       </c>
       <c r="B346" s="13" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="C346" s="13" t="s">
         <v>495</v>
@@ -27872,7 +27937,7 @@
         <v>59</v>
       </c>
       <c r="B347" s="13" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="C347" s="13" t="s">
         <v>495</v>
@@ -27892,7 +27957,7 @@
         <v>59</v>
       </c>
       <c r="B348" s="13" t="s">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="C348" s="13" t="s">
         <v>495</v>
@@ -27912,7 +27977,7 @@
         <v>59</v>
       </c>
       <c r="B349" s="13" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="C349" s="13" t="s">
         <v>495</v>
@@ -27932,7 +27997,7 @@
         <v>59</v>
       </c>
       <c r="B350" s="13" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="C350" s="13" t="s">
         <v>495</v>
@@ -27952,7 +28017,7 @@
         <v>59</v>
       </c>
       <c r="B351" s="13" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="C351" s="13" t="s">
         <v>495</v>
@@ -27972,7 +28037,7 @@
         <v>59</v>
       </c>
       <c r="B352" s="13" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="C352" s="13" t="s">
         <v>495</v>
@@ -27992,7 +28057,7 @@
         <v>59</v>
       </c>
       <c r="B353" s="13" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="C353" s="13" t="s">
         <v>495</v>
@@ -28012,7 +28077,7 @@
         <v>59</v>
       </c>
       <c r="B354" s="13" t="s">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="C354" s="13" t="s">
         <v>495</v>
@@ -28032,7 +28097,7 @@
         <v>59</v>
       </c>
       <c r="B355" s="13" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
       <c r="C355" s="13" t="s">
         <v>495</v>
@@ -28052,7 +28117,7 @@
         <v>59</v>
       </c>
       <c r="B356" s="13" t="s">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="C356" s="13" t="s">
         <v>495</v>
@@ -28072,7 +28137,7 @@
         <v>59</v>
       </c>
       <c r="B357" s="13" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
       <c r="C357" s="13" t="s">
         <v>495</v>
@@ -28092,7 +28157,7 @@
         <v>59</v>
       </c>
       <c r="B358" s="13" t="s">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="C358" s="13" t="s">
         <v>322</v>
@@ -28112,7 +28177,7 @@
         <v>59</v>
       </c>
       <c r="B359" s="13" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="C359" s="13" t="s">
         <v>322</v>
@@ -28132,7 +28197,7 @@
         <v>59</v>
       </c>
       <c r="B360" s="13" t="s">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="C360" s="13" t="s">
         <v>495</v>
@@ -28152,7 +28217,7 @@
         <v>59</v>
       </c>
       <c r="B361" s="13" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="C361" s="13" t="s">
         <v>495</v>
@@ -28172,7 +28237,7 @@
         <v>59</v>
       </c>
       <c r="B362" s="13" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="C362" s="13" t="s">
         <v>495</v>
@@ -28236,7 +28301,7 @@
         <v>310</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1249</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28247,10 +28312,10 @@
         <v>313</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>316</v>
@@ -28259,7 +28324,7 @@
         <v>317</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28273,16 +28338,16 @@
         <v>454</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>323</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28296,16 +28361,16 @@
         <v>454</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28319,16 +28384,16 @@
         <v>445</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>323</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28342,16 +28407,16 @@
         <v>445</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>323</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28365,16 +28430,16 @@
         <v>445</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>323</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
     </row>
   </sheetData>
@@ -28404,10 +28469,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28416,7 +28481,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="B3" s="18" t="n">
         <f aca="false">COUNTA('200V Devices'!C2:C393)</f>
@@ -28425,7 +28490,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="B4" s="18" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"Done (pilot)")</f>
@@ -28434,7 +28499,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"Done")</f>
@@ -28443,7 +28508,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"To do")</f>
@@ -28452,7 +28517,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">COUNTIF('200V Devices'!J2:J393,"Matched from 200V tab")</f>
@@ -28461,7 +28526,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">COUNTA('Not found'!C2:C7)</f>
@@ -28470,7 +28535,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">B3+B8</f>
@@ -28486,7 +28551,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28540,30 +28605,30 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="B18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1271</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">COUNTA('Ports without device'!A2:A362)</f>
@@ -28572,7 +28637,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="B23" s="18" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,"&gt;0")</f>
@@ -28581,7 +28646,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="B24" s="18" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,0)</f>
@@ -28590,7 +28655,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="B25" s="18" t="n">
         <f aca="false">COUNTIF('Ports without device'!H2:H362,"Pilot staff outlet*")</f>
@@ -28599,7 +28664,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="B26" s="18" t="n">
         <f aca="false">COUNTIF('Ports without device'!C2:C362,"None (tagged only)")</f>
@@ -28608,16 +28673,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">COUNT(Review!A5:A130)</f>
@@ -28626,7 +28691,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="B30" s="18" t="n">
         <f aca="false">COUNTA(Review!H5:H130)</f>
@@ -28635,7 +28700,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B31" s="18" t="n">
         <f aca="false">B29-B30</f>

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">Moved to 2700 on 9 Oct (unlisted AV device).</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3J5, device 20:7B:D2:30:98:F3 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3J5, device 20:7B:D2:30:98:F3 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:9B</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">D8:43:AE:B1:6C:A8</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3G16, device 20:7B:D2:30:98:D6 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3G16, device 20:7B:D2:30:98:D6 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">4/1/45</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">5/1/11</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3H2, device 20:7B:D2:30:99:09 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3H2, device 20:7B:D2:30:99:09 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:B0</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3I8, device 20:7B:D2:30:98:AF (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3I8, device 20:7B:D2:30:98:AF (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6E:3C</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">D8:43:AE:B1:6F:04</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3I16, device 20:7B:D2:30:98:D2 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3I16, device 20:7B:D2:30:98:D2 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">5/1/40</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3H14, device 20:7B:D2:30:98:B1 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3H14, device 20:7B:D2:30:98:B1 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">5/1/43</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">5/1/47</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V3H21, device 20:7B:D2:30:99:29 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V3H21, device 20:7B:D2:30:99:29 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">1272,1273,2300,2310,2311,2320,2321</t>
@@ -3509,19 +3509,19 @@
     <t xml:space="preserve">D8:43:AE:B1:6E:06</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V4H22, device 20:7B:D2:30:98:FD (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV outlet 200V4I10, device 20:7B:D2:30:98:EF (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V4H22, device 20:7B:D2:30:98:FD (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outlet 200V4I10, device 20:7B:D2:30:98:EF (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6A:29</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V4J4, device 20:7B:D2:30:98:DB (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV outlet 200V4J14, device 20:7B:D2:30:99:0E (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V4J4, device 20:7B:D2:30:98:DB (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outlet 200V4J14, device 20:7B:D2:30:99:0E (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">00:09:F5:32:D9:F7</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">A0:4A:5E:E7:D5:71</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V4F5, device 20:7B:D2:30:98:DF (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V4F5, device 20:7B:D2:30:98:DF (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">D8:43:AE:B1:6D:56</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">38:4B:76:E0:B0:B1</t>
   </si>
   <si>
-    <t xml:space="preserve">AV outlet 200V4H2, device 20:7B:D2:30:98:C2 (Dycom patching sheet 2025-07-30). To 2700: 200V-av-207bd2-2700-ICX.txt.</t>
+    <t xml:space="preserve">Outlet 200V4H2, device 20:7B:D2:30:98:C2 (Dycom patching sheet 2025-07-30). To 2100 (decision 9 Oct): 200V-207bd2-2100-ICX.txt.</t>
   </si>
   <si>
     <t xml:space="preserve">F8:25:51:CC:2C:76</t>
@@ -21875,7 +21875,7 @@
         <v>322</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E57" s="13"/>
       <c r="F57" s="13" t="n">
@@ -22999,7 +22999,7 @@
         <v>322</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E109" s="13"/>
       <c r="F109" s="13" t="n">
@@ -23145,7 +23145,7 @@
         <v>322</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E116" s="13"/>
       <c r="F116" s="13" t="n">
@@ -23251,7 +23251,7 @@
         <v>322</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E121" s="13"/>
       <c r="F121" s="13" t="n">
@@ -23321,7 +23321,7 @@
         <v>322</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E124" s="13"/>
       <c r="F124" s="13" t="n">
@@ -23363,7 +23363,7 @@
         <v>322</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E126" s="13"/>
       <c r="F126" s="13" t="n">
@@ -23429,7 +23429,7 @@
         <v>322</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E129" s="13"/>
       <c r="F129" s="13" t="n">
@@ -23497,7 +23497,7 @@
         <v>322</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E132" s="13"/>
       <c r="F132" s="13" t="n">
@@ -23539,7 +23539,7 @@
         <v>322</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E134" s="13"/>
       <c r="F134" s="13" t="n">
@@ -23585,7 +23585,7 @@
         <v>322</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E136" s="13"/>
       <c r="F136" s="13" t="n">
@@ -23627,7 +23627,7 @@
         <v>322</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E138" s="13"/>
       <c r="F138" s="13" t="n">
@@ -24283,7 +24283,7 @@
         <v>322</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E170" s="13"/>
       <c r="F170" s="13" t="n">
@@ -24431,7 +24431,7 @@
         <v>322</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="E177" s="13"/>
       <c r="F177" s="13" t="n">

--- a/200V Device Port List.xlsx
+++ b/200V Device Port List.xlsx
@@ -12,15 +12,17 @@
     <sheet name="Old VLAN ports 10 Oct" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="200V Devices" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Switches" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Ports without device" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Not found" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Port clean-up 26 Oct" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Ports without device" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Not found" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Summary" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'200V Devices'!$A$1:$J$393</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Not found'!$A$1:$G$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Not found'!$A$1:$G$7</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Old VLAN ports 10 Oct'!$A$3:$J$240</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Ports without device'!$A$1:$H$362</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Port clean-up 26 Oct'!$A$3:$I$270</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Ports without device'!$A$1:$H$362</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Switches!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7617" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9303" uniqueCount="1408">
   <si>
     <t xml:space="preserve">200V migration: items for review</t>
   </si>
@@ -3523,6 +3525,9 @@
     <t xml:space="preserve">9 Oct 2026 result</t>
   </si>
   <si>
+    <t xml:space="preserve">26 Oct 2026 result</t>
+  </si>
+  <si>
     <t xml:space="preserve">Core / gateway for new VLANs</t>
   </si>
   <si>
@@ -3541,6 +3546,9 @@
     <t xml:space="preserve">Reloaded for system-max 40. WIFIMGMT-IN ACL: added seq 23/24 (SmartZone private IPs) and seq 25 (RADIUS 10.128.131.7) - unplanned, see Review 91 and 107. Saved</t>
   </si>
   <si>
+    <t xml:space="preserve">Not changed (ve 2000 10.21.0.1 is the gateway for the switch management addresses)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Access</t>
   </si>
   <si>
@@ -3553,24 +3561,30 @@
     <t xml:space="preserve">lag 3 (lvl3)</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.22</t>
+    <t xml:space="preserve">10.21.0.27 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.22 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover done, 84 ports. system-max 40 active. Review tab change: 7 ports (5 to 2100, 2 to 2530). Saved. 1/1/48 left on 100. Unlisted AV: 8 ports 1230 -&gt; 2700. 10 Oct: 7 outlets (20:7B:D2:30 devices) 1230 -&gt; 2100. 10 Oct: 3/1/20 (staff PC) 1240 -&gt; 2100</t>
   </si>
   <si>
+    <t xml:space="preserve">Port clean-up: 32 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.27, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved. First Part B attempt rolled back by the reload timer (7:06 pm); second attempt OK.</t>
+  </si>
+  <si>
     <t xml:space="preserve">80_F0_CF_37_FD_84</t>
   </si>
   <si>
     <t xml:space="preserve">lag 2 (lvl4)</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.21</t>
+    <t xml:space="preserve">10.21.0.26 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.21 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover done, 89 ports. system-max 40 active. Confirm APs online. Review tab change: 3/1/7, 3/1/28 to 2100 (no link). 1/1/48 left on 100. Confirm write memory. Unlisted AV: 8 ports 1230 -&gt; 2700. 10 Oct: 6 outlets (20:7B:D2:30 devices) 1230 -&gt; 2100. 10 Oct: 4/1/30 1230 -&gt; 2700, 4/1/19 (Airtame) 1272 -&gt; 2700, 3/1/1 (staff PC) 1240 -&gt; 2100</t>
   </si>
   <si>
+    <t xml:space="preserve">Port clean-up: 54 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.26, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved. SmartZone HTTP 500 until old IP removed and agent restarted.</t>
+  </si>
+  <si>
     <t xml:space="preserve">7 x ICX8200 stack</t>
   </si>
   <si>
@@ -3580,12 +3594,15 @@
     <t xml:space="preserve">lag 1 (lvl6)</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.11</t>
+    <t xml:space="preserve">10.21.0.20 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.11 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover done, 145 ports. system-max 40 active, STP on 2600/2700. Units 3/4 left the stack 20:03 and 22:44 on 9 Oct; out until unit 3 power cycled 13:35 on 10 Oct (unit 3 hangs; TAC/RMA). Saved. Review tab change: 8 ports to 2100. Saved</t>
   </si>
   <si>
+    <t xml:space="preserve">Port clean-up: 144 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.20, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved. 1/1/32 had no MAC when checked.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 x ICX8200-24P</t>
   </si>
   <si>
@@ -3595,12 +3612,15 @@
     <t xml:space="preserve">lag 5 (LT01), LT2-1 ports 1/2/1-1/2/2 to core 1/1/5 + 2/1/5 (LLDP)</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.12</t>
+    <t xml:space="preserve">10.21.0.21 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.12 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover done, 16 ports. system-max 40 active</t>
   </si>
   <si>
+    <t xml:space="preserve">Port clean-up: 5 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.21, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 x ICX7150-C12</t>
   </si>
   <si>
@@ -3610,31 +3630,40 @@
     <t xml:space="preserve">Via LT2-1 port 1/1/23 (their 1/1/12), confirmed by LLDP</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.13</t>
+    <t xml:space="preserve">10.21.0.22 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.13 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">system-max 40 only; no port changes</t>
   </si>
   <si>
+    <t xml:space="preserve">Port clean-up: 11 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.22, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved. 1/1/1 tagged-only with 2000-2953.</t>
+  </si>
+  <si>
     <t xml:space="preserve">10_F0_68_0B_D2_3E</t>
   </si>
   <si>
     <t xml:space="preserve">Via LT2-1 port 1/1/24 (their 1/1/12), confirmed by LLDP</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.14</t>
+    <t xml:space="preserve">10.21.0.23 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.14 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">system-max 40. Review tab change: 1/1/4 to 2100 (no link). Saved</t>
   </si>
   <si>
+    <t xml:space="preserve">Port clean-up: 10 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.23, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved.</t>
+  </si>
+  <si>
     <t xml:space="preserve">10_F0_68_0B_D2_2C</t>
   </si>
   <si>
     <t xml:space="preserve">lag 4 (v08)</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.16</t>
+    <t xml:space="preserve">10.21.0.25 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.16 (ve 100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port clean-up: 10 ports (Trinity column Q, 16 Oct export). Management moved to 10.21.0.25, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved. UPS cards 1/1/7-1/1/9 to 2000 (DHCP); DNS servers added.</t>
   </si>
   <si>
     <t xml:space="preserve">10_F0_68_0B_D2_62</t>
@@ -3643,13 +3672,178 @@
     <t xml:space="preserve">lag 6 (SW6.03)</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.15</t>
+    <t xml:space="preserve">10.21.0.24 (ve 2000, VLAN 2000), from 26 Oct; was 192.168.122.15 (ve 100)</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover done, 6 ports + 1/1/3 and 1/1/9 (added on site). system-max 40 active. Confirm write memory</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: the management IP addresses of the switches are not changing as part of this migration. Access switches stay on VLAN 100 (ve 100, 192.168.122.0/22); the core stays on ve 1960.</t>
+    <t xml:space="preserve">Port clean-up: 1 port (Trinity column Q, 16 Oct export). Management moved to 10.21.0.24, default route via 10.21.0.1, management source ve 2000, old IP removed. Saved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: on 26 Oct 2026 the access switches' management moved from VLAN 100 (ve 100, 192.168.122.0/22) to VLAN 2000 (ve 2000, 10.21.0.20 - .27, gateway 10.21.0.1). The core stays on ve 1960 (10.20.8.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port clean-up from Trinity's switch port export (16 Oct 2026, column Q), applied 26 Oct 2026 on all 8 switches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old untagged VLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tagged VLANs removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New untagged VLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link 16 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAC 16 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1230, 1250, 1271, 1272, 1273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done 26 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1272, 1273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:4F:5E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1212, 1213, 1230, 1240, 1250, 1271, 1272, 1273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (default)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A0:4A:5E:E7:E8:70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:51:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:51:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C0:98:69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C0:9A:AB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:51:DF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C0:9A:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:50:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230, 1212, 1213, 1230, 1250, 1271, 1272, 1273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4C:C5:D9:D0:8D:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:45:3F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48:21:0B:56:AC:A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1212, 1213, 1230, 1250, 1271, 1272, 1273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none (tagged-only 2000-2953)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 3, decision 22 Oct: remove old VLANs only. Port becomes tagged-only with 2000 - 2953 (no untagged VLAN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C0:99:7F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC:B4:80:F1:61:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:09:F5:32:DB:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 2, Trinity 22 Oct: UPS card 00:09:F5:32:DB:15 to 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:09:F5:32:DB:D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 2, Trinity 22 Oct: UPS card 00:09:F5:32:DB:D1 to 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:09:F5:32:DB:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 2, Trinity 22 Oct: UPS card 00:09:F5:32:DB:14 to 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1272, 1273, 2300, 2310, 2311, 2320, 2321, 2900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A0:4A:5E:E7:35:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:51:D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4C:C5:D9:CD:B4:CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 1, Trinity 22 Oct: 20:7B:D2:30:99:15 (200V4H9) to 2100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 1, Trinity 22 Oct: 20:7B:D2:30:99:25 (200V4I17) to 2100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 1, Trinity 22 Oct: 20:7B:D2:30:98:C1 (200V3J14) to 2100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C:1A:DF:C2:51:C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A0:4A:5E:E7:D5:7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230</t>
   </si>
   <si>
     <t xml:space="preserve">Untagged VLAN</t>
@@ -3664,9 +3858,6 @@
     <t xml:space="preserve">MAC(s) seen</t>
   </si>
   <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
     <t xml:space="preserve">None (tagged only)</t>
   </si>
   <si>
@@ -3685,9 +3876,6 @@
     <t xml:space="preserve">00:50:56:05:43:F1</t>
   </si>
   <si>
-    <t xml:space="preserve">48:21:0B:56:AC:A4</t>
-  </si>
-  <si>
     <t xml:space="preserve">LLDP: CLA-TAN3130059J (NUC, MAC 48:21:0B:56:AC:A4), not in device list</t>
   </si>
   <si>
@@ -3712,9 +3900,6 @@
     <t xml:space="preserve">1240 (200v_staff)</t>
   </si>
   <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
     <t xml:space="preserve">d4:a2:cd:e1:dd:0e</t>
   </si>
   <si>
@@ -3724,9 +3909,6 @@
     <t xml:space="preserve">100,1230,1272</t>
   </si>
   <si>
-    <t xml:space="preserve">1230</t>
-  </si>
-  <si>
     <t xml:space="preserve">F8:25:51:CB:8C:76</t>
   </si>
   <si>
@@ -3962,12 +4144,6 @@
   </si>
   <si>
     <t xml:space="preserve">1C:1A:DF:C2:44:7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1273</t>
   </si>
   <si>
     <t xml:space="preserve">Already on 2010</t>
@@ -4109,7 +4285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4172,6 +4348,13 @@
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -4293,7 +4476,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4350,7 +4533,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4374,7 +4557,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4552,6 +4743,10 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -26295,7 +26490,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="28"/>
@@ -26305,7 +26500,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26336,34 +26531,40 @@
       <c r="I1" s="4" t="s">
         <v>1156</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
         <v>219</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>1162</v>
+        <v>1163</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26371,16 +26572,16 @@
         <v>95</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="F3" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A3)</f>
@@ -26391,10 +26592,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>1168</v>
+        <v>1170</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26402,16 +26606,16 @@
         <v>135</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A4)</f>
@@ -26422,10 +26626,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>1172</v>
+        <v>1175</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>1176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26433,16 +26640,16 @@
         <v>59</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="F5" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A5)</f>
@@ -26453,10 +26660,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>1177</v>
+        <v>1181</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26464,16 +26674,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A6)</f>
@@ -26484,10 +26694,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1182</v>
+        <v>1187</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>1188</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26495,16 +26708,16 @@
         <v>233</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A7)</f>
@@ -26515,10 +26728,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>1187</v>
+        <v>1193</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26526,16 +26742,16 @@
         <v>88</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A8)</f>
@@ -26546,10 +26762,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>1191</v>
+        <v>1198</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>1199</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26557,16 +26776,16 @@
         <v>76</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A9)</f>
@@ -26577,10 +26796,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>1187</v>
+        <v>1193</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26588,16 +26810,16 @@
         <v>70</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">COUNTIF('200V Devices'!E2:E393,A10)</f>
@@ -26608,33 +26830,36 @@
         <v>0</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>1198</v>
+        <v>1207</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>1208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20" t="n">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21" t="n">
         <f aca="false">SUM(F2:F10)</f>
         <v>392</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <f aca="false">SUM(G2:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="20"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1199</v>
+        <v>1209</v>
       </c>
     </row>
   </sheetData>
@@ -26651,6 +26876,5604 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I270"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="22" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A202" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A210" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A211" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A220" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A221" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A222" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A223" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A224" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A225" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A226" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A227" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A228" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A229" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A230" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A234" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A240" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A244" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A246" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A247" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A248" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A250" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A252" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A253" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A254" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I254" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A255" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A256" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A257" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A258" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A259" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I259" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A260" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I260" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A261" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I261" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A262" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I262" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A263" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I263" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A264" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I264" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A265" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I265" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A266" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I266" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A267" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I267" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A269" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A270" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I270"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -26676,22 +32499,22 @@
         <v>5</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1200</v>
+        <v>1264</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>532</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1201</v>
+        <v>1265</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1202</v>
+        <v>1266</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1203</v>
+        <v>1267</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26915,27 +32738,27 @@
       <c r="H12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>1207</v>
-      </c>
-      <c r="F13" s="21" t="n">
+      <c r="C13" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21" t="s">
-        <v>1208</v>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26952,7 +32775,7 @@
         <v>538</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>1209</v>
+        <v>1272</v>
       </c>
       <c r="F14" s="19" t="n">
         <v>0</v>
@@ -26981,26 +32804,26 @@
       <c r="H15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22" t="n">
+      <c r="C16" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="22" t="s">
-        <v>1210</v>
-      </c>
-      <c r="H16" s="22"/>
+      <c r="G16" s="24" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
@@ -27023,27 +32846,27 @@
       <c r="H17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22" t="n">
+      <c r="C18" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="22" t="s">
-        <v>1211</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>1212</v>
+      <c r="G18" s="24" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>1274</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27067,55 +32890,55 @@
       <c r="H19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="23" t="s">
         <v>616</v>
       </c>
-      <c r="C20" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F20" s="21" t="n">
+      <c r="C20" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F20" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="21" t="s">
-        <v>1214</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>1215</v>
+      <c r="G20" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>1277</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="23" t="s">
         <v>618</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F21" s="21" t="n">
+      <c r="C21" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F21" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="21" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>1217</v>
+      <c r="G21" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>1279</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27132,7 +32955,7 @@
         <v>345</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>1218</v>
+        <v>1280</v>
       </c>
       <c r="F22" s="19" t="n">
         <v>0</v>
@@ -27341,27 +33164,27 @@
       <c r="H32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F33" s="21" t="n">
+      <c r="C33" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F33" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21" t="s">
-        <v>1208</v>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27372,13 +33195,13 @@
         <v>213</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F34" s="19" t="n">
         <v>0</v>
@@ -27394,13 +33217,13 @@
         <v>197</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F35" s="19" t="n">
         <v>0</v>
@@ -27416,13 +33239,13 @@
         <v>93</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F36" s="19" t="n">
         <v>0</v>
@@ -27438,22 +33261,22 @@
         <v>89</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>345</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F37" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1221</v>
+        <v>1282</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27464,13 +33287,13 @@
         <v>422</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F38" s="19" t="n">
         <v>0</v>
@@ -27486,13 +33309,13 @@
         <v>14</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F39" s="19" t="n">
         <v>0</v>
@@ -27508,13 +33331,13 @@
         <v>20</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F40" s="19" t="n">
         <v>0</v>
@@ -27530,13 +33353,13 @@
         <v>23</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F41" s="19" t="n">
         <v>0</v>
@@ -27552,13 +33375,13 @@
         <v>71</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F42" s="19" t="n">
         <v>0</v>
@@ -27574,13 +33397,13 @@
         <v>26</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F43" s="19" t="n">
         <v>0</v>
@@ -27596,13 +33419,13 @@
         <v>29</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>345</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F44" s="19" t="n">
         <v>0</v>
@@ -27611,51 +33434,51 @@
       <c r="H44" s="19"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F45" s="21" t="n">
+      <c r="C45" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F45" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21" t="s">
-        <v>1208</v>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>1223</v>
-      </c>
-      <c r="F46" s="21" t="n">
+      <c r="C46" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F46" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21" t="s">
-        <v>1208</v>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27666,22 +33489,22 @@
         <v>93</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="D47" s="17" t="s">
         <v>331</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F47" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1225</v>
+        <v>1285</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>1226</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27692,46 +33515,46 @@
         <v>71</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>331</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F48" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1227</v>
+        <v>1287</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>1228</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>1220</v>
-      </c>
-      <c r="F49" s="21" t="n">
+      <c r="C49" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21" t="s">
-        <v>1208</v>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27742,7 +33565,7 @@
         <v>29</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>538</v>
@@ -27755,27 +33578,27 @@
       <c r="H50" s="19"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>1220</v>
-      </c>
-      <c r="F51" s="21" t="n">
+      <c r="C51" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21" t="s">
-        <v>1208</v>
+      <c r="G51" s="23"/>
+      <c r="H51" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27792,7 +33615,7 @@
         <v>538</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>1209</v>
+        <v>1272</v>
       </c>
       <c r="F52" s="19" t="n">
         <v>0</v>
@@ -27821,26 +33644,26 @@
       <c r="H53" s="19"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B54" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22" t="n">
+      <c r="E54" s="24"/>
+      <c r="F54" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="22" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H54" s="22"/>
+      <c r="G54" s="24" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H54" s="24"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
@@ -27880,10 +33703,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>1230</v>
+        <v>1290</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27905,7 +33728,7 @@
       </c>
       <c r="G57" s="17"/>
       <c r="H57" s="17" t="s">
-        <v>1232</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27966,10 +33789,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>1233</v>
+        <v>1293</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28030,10 +33853,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>1234</v>
+        <v>1294</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28195,7 +34018,7 @@
       </c>
       <c r="G71" s="17"/>
       <c r="H71" s="17" t="s">
-        <v>1235</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28256,10 +34079,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>1236</v>
+        <v>1296</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28280,10 +34103,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>1237</v>
+        <v>1297</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28304,10 +34127,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>1238</v>
+        <v>1298</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28328,10 +34151,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>1239</v>
+        <v>1299</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28345,7 +34168,7 @@
         <v>345</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E78" s="17"/>
       <c r="F78" s="17" t="n">
@@ -28353,7 +34176,7 @@
       </c>
       <c r="G78" s="17"/>
       <c r="H78" s="17" t="s">
-        <v>1241</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28367,7 +34190,7 @@
         <v>345</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E79" s="17"/>
       <c r="F79" s="17" t="n">
@@ -28375,7 +34198,7 @@
       </c>
       <c r="G79" s="17"/>
       <c r="H79" s="17" t="s">
-        <v>1242</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28389,7 +34212,7 @@
         <v>345</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E80" s="17"/>
       <c r="F80" s="17" t="n">
@@ -28397,7 +34220,7 @@
       </c>
       <c r="G80" s="17"/>
       <c r="H80" s="17" t="s">
-        <v>1243</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28411,7 +34234,7 @@
         <v>345</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E81" s="17"/>
       <c r="F81" s="17" t="n">
@@ -28419,7 +34242,7 @@
       </c>
       <c r="G81" s="17"/>
       <c r="H81" s="17" t="s">
-        <v>1244</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28433,7 +34256,7 @@
         <v>345</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E82" s="17"/>
       <c r="F82" s="17" t="n">
@@ -28441,7 +34264,7 @@
       </c>
       <c r="G82" s="17"/>
       <c r="H82" s="17" t="s">
-        <v>1245</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28455,7 +34278,7 @@
         <v>345</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E83" s="17"/>
       <c r="F83" s="17" t="n">
@@ -28463,7 +34286,7 @@
       </c>
       <c r="G83" s="17"/>
       <c r="H83" s="17" t="s">
-        <v>1246</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28497,7 +34320,7 @@
         <v>345</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17" t="n">
@@ -28505,7 +34328,7 @@
       </c>
       <c r="G85" s="17"/>
       <c r="H85" s="17" t="s">
-        <v>1247</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28519,7 +34342,7 @@
         <v>345</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E86" s="17"/>
       <c r="F86" s="17" t="n">
@@ -28527,7 +34350,7 @@
       </c>
       <c r="G86" s="17"/>
       <c r="H86" s="17" t="s">
-        <v>1248</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28541,7 +34364,7 @@
         <v>345</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17" t="n">
@@ -28549,7 +34372,7 @@
       </c>
       <c r="G87" s="17"/>
       <c r="H87" s="17" t="s">
-        <v>1249</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28563,7 +34386,7 @@
         <v>345</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E88" s="17"/>
       <c r="F88" s="17" t="n">
@@ -28571,7 +34394,7 @@
       </c>
       <c r="G88" s="17"/>
       <c r="H88" s="17" t="s">
-        <v>1250</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28585,7 +34408,7 @@
         <v>345</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17" t="n">
@@ -28593,7 +34416,7 @@
       </c>
       <c r="G89" s="17"/>
       <c r="H89" s="17" t="s">
-        <v>1251</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28607,7 +34430,7 @@
         <v>345</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E90" s="17"/>
       <c r="F90" s="17" t="n">
@@ -28615,7 +34438,7 @@
       </c>
       <c r="G90" s="17"/>
       <c r="H90" s="17" t="s">
-        <v>1252</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28629,7 +34452,7 @@
         <v>345</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="17" t="n">
@@ -28637,7 +34460,7 @@
       </c>
       <c r="G91" s="17"/>
       <c r="H91" s="17" t="s">
-        <v>1253</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28651,17 +34474,17 @@
         <v>345</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>1254</v>
+        <v>1314</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>1255</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28675,7 +34498,7 @@
         <v>345</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E93" s="17"/>
       <c r="F93" s="17" t="n">
@@ -28683,7 +34506,7 @@
       </c>
       <c r="G93" s="17"/>
       <c r="H93" s="17" t="s">
-        <v>1256</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28697,7 +34520,7 @@
         <v>345</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="17" t="n">
@@ -28705,7 +34528,7 @@
       </c>
       <c r="G94" s="17"/>
       <c r="H94" s="17" t="s">
-        <v>1257</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28719,7 +34542,7 @@
         <v>345</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E95" s="17"/>
       <c r="F95" s="17" t="n">
@@ -28727,7 +34550,7 @@
       </c>
       <c r="G95" s="17"/>
       <c r="H95" s="17" t="s">
-        <v>1258</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28741,7 +34564,7 @@
         <v>345</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="17" t="n">
@@ -28749,7 +34572,7 @@
       </c>
       <c r="G96" s="17"/>
       <c r="H96" s="17" t="s">
-        <v>1259</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28763,7 +34586,7 @@
         <v>345</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E97" s="17"/>
       <c r="F97" s="17" t="n">
@@ -28771,7 +34594,7 @@
       </c>
       <c r="G97" s="17"/>
       <c r="H97" s="17" t="s">
-        <v>1260</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28785,7 +34608,7 @@
         <v>345</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E98" s="17"/>
       <c r="F98" s="17" t="n">
@@ -28793,7 +34616,7 @@
       </c>
       <c r="G98" s="17"/>
       <c r="H98" s="17" t="s">
-        <v>1261</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28807,7 +34630,7 @@
         <v>345</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E99" s="17"/>
       <c r="F99" s="17" t="n">
@@ -28815,7 +34638,7 @@
       </c>
       <c r="G99" s="17"/>
       <c r="H99" s="17" t="s">
-        <v>1262</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28829,7 +34652,7 @@
         <v>345</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="E100" s="17"/>
       <c r="F100" s="17" t="n">
@@ -28837,7 +34660,7 @@
       </c>
       <c r="G100" s="17"/>
       <c r="H100" s="17" t="s">
-        <v>1263</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28958,10 +34781,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>1264</v>
+        <v>1324</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28982,10 +34805,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>1265</v>
+        <v>1325</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29006,10 +34829,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>1266</v>
+        <v>1326</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29031,7 +34854,7 @@
       </c>
       <c r="G109" s="17"/>
       <c r="H109" s="17" t="s">
-        <v>1267</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29072,10 +34895,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>1268</v>
+        <v>1328</v>
       </c>
       <c r="H111" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29177,7 +35000,7 @@
       </c>
       <c r="G116" s="17"/>
       <c r="H116" s="17" t="s">
-        <v>1269</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29238,10 +35061,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>1270</v>
+        <v>1330</v>
       </c>
       <c r="H119" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29283,7 +35106,7 @@
       </c>
       <c r="G121" s="17"/>
       <c r="H121" s="17" t="s">
-        <v>1271</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29304,10 +35127,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>1272</v>
+        <v>1332</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29328,10 +35151,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>1273</v>
+        <v>1333</v>
       </c>
       <c r="H123" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29353,7 +35176,7 @@
       </c>
       <c r="G124" s="17"/>
       <c r="H124" s="17" t="s">
-        <v>1274</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29395,7 +35218,7 @@
       </c>
       <c r="G126" s="17"/>
       <c r="H126" s="17" t="s">
-        <v>1275</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29436,10 +35259,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>1276</v>
+        <v>1336</v>
       </c>
       <c r="H128" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29461,7 +35284,7 @@
       </c>
       <c r="G129" s="17"/>
       <c r="H129" s="17" t="s">
-        <v>1277</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29478,7 +35301,7 @@
         <v>538</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>1278</v>
+        <v>1338</v>
       </c>
       <c r="F130" s="19" t="n">
         <v>0</v>
@@ -29504,10 +35327,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>1279</v>
+        <v>1339</v>
       </c>
       <c r="H131" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29529,7 +35352,7 @@
       </c>
       <c r="G132" s="17"/>
       <c r="H132" s="17" t="s">
-        <v>1280</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29571,7 +35394,7 @@
       </c>
       <c r="G134" s="17"/>
       <c r="H134" s="17" t="s">
-        <v>1281</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29592,10 +35415,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>1282</v>
+        <v>1342</v>
       </c>
       <c r="H135" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29617,7 +35440,7 @@
       </c>
       <c r="G136" s="17"/>
       <c r="H136" s="17" t="s">
-        <v>1283</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29659,30 +35482,30 @@
       </c>
       <c r="G138" s="17"/>
       <c r="H138" s="17" t="s">
-        <v>1284</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="22" t="s">
+      <c r="A139" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B139" s="22" t="s">
+      <c r="B139" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C139" s="22" t="s">
+      <c r="C139" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="D139" s="22" t="s">
+      <c r="D139" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="E139" s="22"/>
-      <c r="F139" s="22" t="n">
+      <c r="E139" s="24"/>
+      <c r="F139" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G139" s="22" t="s">
-        <v>1285</v>
-      </c>
-      <c r="H139" s="22"/>
+      <c r="G139" s="24" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H139" s="24"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="19" t="s">
@@ -29762,10 +35585,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>1286</v>
+        <v>1346</v>
       </c>
       <c r="H143" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29787,7 +35610,7 @@
       </c>
       <c r="G144" s="17"/>
       <c r="H144" s="17" t="s">
-        <v>1235</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29848,10 +35671,10 @@
         <v>1</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>1287</v>
+        <v>1347</v>
       </c>
       <c r="H147" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30052,10 +35875,10 @@
         <v>1</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>1288</v>
+        <v>1348</v>
       </c>
       <c r="H157" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30317,7 +36140,7 @@
       </c>
       <c r="G170" s="17"/>
       <c r="H170" s="17" t="s">
-        <v>1289</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30338,10 +36161,10 @@
         <v>1</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>1290</v>
+        <v>1350</v>
       </c>
       <c r="H171" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30442,10 +36265,10 @@
         <v>1</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>1291</v>
+        <v>1351</v>
       </c>
       <c r="H176" s="17" t="s">
-        <v>1292</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30467,7 +36290,7 @@
       </c>
       <c r="G177" s="17"/>
       <c r="H177" s="17" t="s">
-        <v>1293</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30548,10 +36371,10 @@
         <v>1</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>1294</v>
+        <v>1354</v>
       </c>
       <c r="H181" s="17" t="s">
-        <v>1295</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30732,10 +36555,10 @@
         <v>1</v>
       </c>
       <c r="G190" s="17" t="s">
-        <v>1296</v>
+        <v>1356</v>
       </c>
       <c r="H190" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30756,10 +36579,10 @@
         <v>1</v>
       </c>
       <c r="G191" s="17" t="s">
-        <v>1297</v>
+        <v>1357</v>
       </c>
       <c r="H191" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30840,10 +36663,10 @@
         <v>1</v>
       </c>
       <c r="G195" s="17" t="s">
-        <v>1298</v>
+        <v>1358</v>
       </c>
       <c r="H195" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30904,10 +36727,10 @@
         <v>1</v>
       </c>
       <c r="G198" s="17" t="s">
-        <v>1299</v>
+        <v>1359</v>
       </c>
       <c r="H198" s="17" t="s">
-        <v>1231</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31024,7 +36847,7 @@
         <v>345</v>
       </c>
       <c r="E204" s="19" t="s">
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="F204" s="19" t="n">
         <v>0</v>
@@ -31046,7 +36869,7 @@
         <v>345</v>
       </c>
       <c r="E205" s="19" t="s">
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="F205" s="19" t="n">
         <v>0</v>
@@ -31055,27 +36878,27 @@
       <c r="H205" s="19"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B206" s="21" t="s">
+      <c r="A206" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B206" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C206" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D206" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E206" s="21" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F206" s="21" t="n">
+      <c r="C206" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D206" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E206" s="23" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F206" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G206" s="21"/>
-      <c r="H206" s="21" t="s">
-        <v>1208</v>
+      <c r="G206" s="23"/>
+      <c r="H206" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31092,7 +36915,7 @@
         <v>345</v>
       </c>
       <c r="E207" s="19" t="s">
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="F207" s="19" t="n">
         <v>0</v>
@@ -31114,7 +36937,7 @@
         <v>345</v>
       </c>
       <c r="E208" s="19" t="s">
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="F208" s="19" t="n">
         <v>0</v>
@@ -31123,27 +36946,27 @@
       <c r="H208" s="19"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B209" s="21" t="s">
+      <c r="A209" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B209" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C209" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D209" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E209" s="21" t="s">
-        <v>1300</v>
-      </c>
-      <c r="F209" s="21" t="n">
+      <c r="C209" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D209" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E209" s="23" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F209" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G209" s="21"/>
-      <c r="H209" s="21" t="s">
-        <v>1208</v>
+      <c r="G209" s="23"/>
+      <c r="H209" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31160,7 +36983,7 @@
         <v>345</v>
       </c>
       <c r="E210" s="19" t="s">
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="F210" s="19" t="n">
         <v>0</v>
@@ -31182,7 +37005,7 @@
         <v>345</v>
       </c>
       <c r="E211" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F211" s="19" t="n">
         <v>0</v>
@@ -31204,7 +37027,7 @@
         <v>345</v>
       </c>
       <c r="E212" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F212" s="19" t="n">
         <v>0</v>
@@ -31226,7 +37049,7 @@
         <v>345</v>
       </c>
       <c r="E213" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F213" s="19" t="n">
         <v>0</v>
@@ -31248,16 +37071,16 @@
         <v>345</v>
       </c>
       <c r="E214" s="17" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F214" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G214" s="17" t="s">
-        <v>1303</v>
+        <v>1363</v>
       </c>
       <c r="H214" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31274,7 +37097,7 @@
         <v>345</v>
       </c>
       <c r="E215" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F215" s="19" t="n">
         <v>0</v>
@@ -31296,7 +37119,7 @@
         <v>345</v>
       </c>
       <c r="E216" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F216" s="19" t="n">
         <v>0</v>
@@ -31318,7 +37141,7 @@
         <v>345</v>
       </c>
       <c r="E217" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F217" s="19" t="n">
         <v>0</v>
@@ -31340,7 +37163,7 @@
         <v>538</v>
       </c>
       <c r="E218" s="19" t="s">
-        <v>1209</v>
+        <v>1272</v>
       </c>
       <c r="F218" s="19" t="n">
         <v>0</v>
@@ -31362,7 +37185,7 @@
         <v>345</v>
       </c>
       <c r="E219" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F219" s="19" t="n">
         <v>0</v>
@@ -31384,7 +37207,7 @@
         <v>345</v>
       </c>
       <c r="E220" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F220" s="19" t="n">
         <v>0</v>
@@ -31406,7 +37229,7 @@
         <v>345</v>
       </c>
       <c r="E221" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F221" s="19" t="n">
         <v>0</v>
@@ -31428,7 +37251,7 @@
         <v>345</v>
       </c>
       <c r="E222" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F222" s="19" t="n">
         <v>0</v>
@@ -31450,7 +37273,7 @@
         <v>345</v>
       </c>
       <c r="E223" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F223" s="19" t="n">
         <v>0</v>
@@ -31472,7 +37295,7 @@
         <v>345</v>
       </c>
       <c r="E224" s="19" t="s">
-        <v>1304</v>
+        <v>1227</v>
       </c>
       <c r="F224" s="19" t="n">
         <v>0</v>
@@ -31494,7 +37317,7 @@
         <v>345</v>
       </c>
       <c r="E225" s="19" t="s">
-        <v>1302</v>
+        <v>1362</v>
       </c>
       <c r="F225" s="19" t="n">
         <v>0</v>
@@ -31516,7 +37339,7 @@
         <v>345</v>
       </c>
       <c r="E226" s="19" t="s">
-        <v>1305</v>
+        <v>1228</v>
       </c>
       <c r="F226" s="19" t="n">
         <v>0</v>
@@ -31745,27 +37568,27 @@
       <c r="H237" s="19"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B238" s="21" t="s">
+      <c r="A238" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B238" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="C238" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D238" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E238" s="21" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F238" s="21" t="n">
+      <c r="C238" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D238" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E238" s="23" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F238" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G238" s="21"/>
-      <c r="H238" s="21" t="s">
-        <v>1208</v>
+      <c r="G238" s="23"/>
+      <c r="H238" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31779,7 +37602,7 @@
         <v>538</v>
       </c>
       <c r="D239" s="19" t="s">
-        <v>1306</v>
+        <v>1364</v>
       </c>
       <c r="E239" s="19"/>
       <c r="F239" s="19" t="n">
@@ -31826,10 +37649,10 @@
         <v>1</v>
       </c>
       <c r="G241" s="17" t="s">
-        <v>1307</v>
+        <v>1365</v>
       </c>
       <c r="H241" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32090,10 +37913,10 @@
         <v>1</v>
       </c>
       <c r="G254" s="17" t="s">
-        <v>1308</v>
+        <v>1366</v>
       </c>
       <c r="H254" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32754,10 +38577,10 @@
         <v>1</v>
       </c>
       <c r="G287" s="17" t="s">
-        <v>1309</v>
+        <v>1367</v>
       </c>
       <c r="H287" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32834,7 +38657,7 @@
         <v>538</v>
       </c>
       <c r="E291" s="19" t="s">
-        <v>1310</v>
+        <v>1368</v>
       </c>
       <c r="F291" s="19" t="n">
         <v>0</v>
@@ -33060,10 +38883,10 @@
         <v>1</v>
       </c>
       <c r="G302" s="17" t="s">
-        <v>1311</v>
+        <v>1369</v>
       </c>
       <c r="H302" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33384,10 +39207,10 @@
         <v>1</v>
       </c>
       <c r="G318" s="17" t="s">
-        <v>1312</v>
+        <v>1370</v>
       </c>
       <c r="H318" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33488,10 +39311,10 @@
         <v>1</v>
       </c>
       <c r="G323" s="17" t="s">
-        <v>1313</v>
+        <v>1371</v>
       </c>
       <c r="H323" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33592,10 +39415,10 @@
         <v>1</v>
       </c>
       <c r="G328" s="17" t="s">
-        <v>1314</v>
+        <v>1372</v>
       </c>
       <c r="H328" s="17" t="s">
-        <v>1222</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33779,27 +39602,27 @@
       <c r="H337" s="19"/>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A338" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B338" s="21" t="s">
+      <c r="A338" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B338" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="C338" s="21" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D338" s="21" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E338" s="21" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F338" s="21" t="n">
+      <c r="C338" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D338" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E338" s="23" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F338" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G338" s="21"/>
-      <c r="H338" s="21" t="s">
-        <v>1208</v>
+      <c r="G338" s="23"/>
+      <c r="H338" s="23" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34295,7 +40118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -34331,7 +40154,7 @@
         <v>532</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1315</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34342,10 +40165,10 @@
         <v>535</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>1316</v>
+        <v>1374</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>1317</v>
+        <v>1375</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>325</v>
@@ -34354,7 +40177,7 @@
         <v>538</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34368,16 +40191,16 @@
         <v>660</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>1319</v>
+        <v>1377</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>1320</v>
+        <v>1378</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>331</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34391,16 +40214,16 @@
         <v>660</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>1321</v>
+        <v>1379</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>1320</v>
+        <v>1378</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>331</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34414,16 +40237,16 @@
         <v>653</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>1322</v>
+        <v>1380</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>1320</v>
+        <v>1378</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>331</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34437,16 +40260,16 @@
         <v>653</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>1323</v>
+        <v>1381</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>1320</v>
+        <v>1378</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>331</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34460,16 +40283,16 @@
         <v>653</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>1324</v>
+        <v>1382</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>1320</v>
+        <v>1378</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>331</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
   </sheetData>
@@ -34485,7 +40308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -34499,10 +40322,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>1325</v>
+        <v>1383</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1326</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34511,7 +40334,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1327</v>
+        <v>1385</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTA('200V Devices'!C2:C393)</f>
@@ -34520,7 +40343,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>1328</v>
+        <v>1386</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"Done (pilot)")</f>
@@ -34529,7 +40352,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>1329</v>
+        <v>1387</v>
       </c>
       <c r="B5" s="15" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"Done")</f>
@@ -34538,7 +40361,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>1330</v>
+        <v>1388</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">COUNTIF('200V Devices'!I2:I393,"To do")</f>
@@ -34547,7 +40370,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>1331</v>
+        <v>1389</v>
       </c>
       <c r="B7" s="15" t="n">
         <f aca="false">COUNTIF('200V Devices'!J2:J393,"Matched from 200V tab")</f>
@@ -34556,7 +40379,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>1332</v>
+        <v>1390</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">COUNTA('Not found'!C2:C7)</f>
@@ -34565,7 +40388,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1333</v>
+        <v>1391</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">B3+B8</f>
@@ -34581,7 +40404,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1334</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34635,30 +40458,30 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1335</v>
+        <v>1393</v>
       </c>
       <c r="B18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>1336</v>
+      <c r="A19" s="25" t="s">
+        <v>1394</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1337</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>1338</v>
+      <c r="A20" s="26" t="s">
+        <v>1396</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>1339</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1340</v>
+        <v>1398</v>
       </c>
       <c r="B22" s="15" t="n">
         <f aca="false">COUNTA('Ports without device'!A2:A362)</f>
@@ -34667,7 +40490,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>1341</v>
+        <v>1399</v>
       </c>
       <c r="B23" s="15" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,"&gt;0")</f>
@@ -34676,7 +40499,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>1342</v>
+        <v>1400</v>
       </c>
       <c r="B24" s="15" t="n">
         <f aca="false">COUNTIF('Ports without device'!F2:F362,0)</f>
@@ -34685,7 +40508,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>1343</v>
+        <v>1401</v>
       </c>
       <c r="B25" s="15" t="n">
         <f aca="false">COUNTIF('Ports without device'!H2:H362,"Pilot staff outlet*")</f>
@@ -34694,7 +40517,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>1344</v>
+        <v>1402</v>
       </c>
       <c r="B26" s="15" t="n">
         <f aca="false">COUNTIF('Ports without device'!C2:C362,"None (tagged only)")</f>
@@ -34702,17 +40525,17 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
-        <v>1345</v>
+      <c r="A27" s="27" t="s">
+        <v>1403</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>1346</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1347</v>
+        <v>1405</v>
       </c>
       <c r="B29" s="15" t="n">
         <f aca="false">COUNT(Review!A5:A130)</f>
@@ -34721,7 +40544,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>1348</v>
+        <v>1406</v>
       </c>
       <c r="B30" s="15" t="n">
         <f aca="false">COUNTA(Review!H5:H130)</f>
@@ -34730,7 +40553,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>1349</v>
+        <v>1407</v>
       </c>
       <c r="B31" s="15" t="n">
         <f aca="false">B29-B30</f>
